--- a/backend/excel-files/sample_bulk_payments.xlsx
+++ b/backend/excel-files/sample_bulk_payments.xlsx
@@ -444,19 +444,19 @@
         <v>UMaT/PG/0001/22</v>
       </c>
       <c r="B2" t="str">
-        <v>Mensah Frimpong</v>
+        <v>Yaa Nkrumah</v>
       </c>
       <c r="C2">
-        <v>8200</v>
+        <v>7700</v>
       </c>
       <c r="D2">
-        <v>8200</v>
+        <v>6900</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F2" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G2" t="str">
         <v>Second</v>
@@ -465,7 +465,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I2" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="3">
@@ -473,22 +473,22 @@
         <v>UMaT/PG/0002/22</v>
       </c>
       <c r="B3" t="str">
-        <v>Kodwo Agyemang</v>
+        <v>Ato Owusu</v>
       </c>
       <c r="C3">
-        <v>8600</v>
+        <v>11100</v>
       </c>
       <c r="D3">
-        <v>8600</v>
+        <v>11100</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G3" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H3" t="str">
         <v>Bank Transfer</v>
@@ -502,22 +502,22 @@
         <v>UMaT/PG/0003/22</v>
       </c>
       <c r="B4" t="str">
-        <v>Ama Sarpong</v>
+        <v>Mensah Agyei</v>
       </c>
       <c r="C4">
-        <v>9800</v>
+        <v>10100</v>
       </c>
       <c r="D4">
-        <v>9800</v>
+        <v>10100</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G4" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H4" t="str">
         <v>Bank Transfer</v>
@@ -531,28 +531,28 @@
         <v>UMaT/PG/0004/22</v>
       </c>
       <c r="B5" t="str">
-        <v>Kwaku Agyei</v>
+        <v>Afi Amankwah</v>
       </c>
       <c r="C5">
-        <v>12200</v>
+        <v>7700</v>
       </c>
       <c r="D5">
-        <v>6300</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>5900</v>
+        <v>7700</v>
       </c>
       <c r="F5" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G5" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H5" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I5" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="6">
@@ -560,28 +560,28 @@
         <v>UMaT/PG/0005/22</v>
       </c>
       <c r="B6" t="str">
-        <v>Yaw Sarpong</v>
+        <v>Kwame Danquah</v>
       </c>
       <c r="C6">
-        <v>7400</v>
+        <v>9300</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="E6">
-        <v>7400</v>
+        <v>5600</v>
       </c>
       <c r="F6" t="str">
         <v>2024/2025</v>
       </c>
       <c r="G6" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H6" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I6" t="str">
-        <v>Unpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="7">
@@ -589,22 +589,22 @@
         <v>UMaT/PG/0006/22</v>
       </c>
       <c r="B7" t="str">
-        <v>Kwame Sarpong</v>
+        <v>Kwaku Gyasi</v>
       </c>
       <c r="C7">
-        <v>7400</v>
+        <v>12400</v>
       </c>
       <c r="D7">
-        <v>2300</v>
+        <v>11700</v>
       </c>
       <c r="E7">
-        <v>5100</v>
+        <v>700</v>
       </c>
       <c r="F7" t="str">
         <v>2024/2025</v>
       </c>
       <c r="G7" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H7" t="str">
         <v>Bank Transfer</v>
@@ -618,28 +618,28 @@
         <v>UMaT/PG/0007/22</v>
       </c>
       <c r="B8" t="str">
-        <v>Afi Agyemang</v>
+        <v>Abena Owusu</v>
       </c>
       <c r="C8">
-        <v>7900</v>
+        <v>10200</v>
       </c>
       <c r="D8">
-        <v>7900</v>
+        <v>4900</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="F8" t="str">
         <v>2024/2025</v>
       </c>
       <c r="G8" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H8" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I8" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="9">
@@ -647,28 +647,28 @@
         <v>UMaT/PG/0008/22</v>
       </c>
       <c r="B9" t="str">
-        <v>Kwesi Addo</v>
+        <v>Kwabena Ofori</v>
       </c>
       <c r="C9">
-        <v>10700</v>
+        <v>6800</v>
       </c>
       <c r="D9">
-        <v>3600</v>
+        <v>6800</v>
       </c>
       <c r="E9">
-        <v>7100</v>
+        <v>0</v>
       </c>
       <c r="F9" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G9" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H9" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I9" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="10">
@@ -676,16 +676,16 @@
         <v>UMaT/PG/0009/22</v>
       </c>
       <c r="B10" t="str">
-        <v>Efua Acheampong</v>
+        <v>Panyin Darko</v>
       </c>
       <c r="C10">
-        <v>10000</v>
+        <v>11600</v>
       </c>
       <c r="D10">
-        <v>11200</v>
+        <v>4100</v>
       </c>
       <c r="E10">
-        <v>-1200</v>
+        <v>7500</v>
       </c>
       <c r="F10" t="str">
         <v>2024/2025</v>
@@ -697,7 +697,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I10" t="str">
-        <v>Overpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="11">
@@ -705,28 +705,28 @@
         <v>UMaT/PG/0010/22</v>
       </c>
       <c r="B11" t="str">
-        <v>Mensah Opoku</v>
+        <v>Akosua Frimpong</v>
       </c>
       <c r="C11">
-        <v>7800</v>
+        <v>10900</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>9400</v>
       </c>
       <c r="E11">
-        <v>7800</v>
+        <v>1500</v>
       </c>
       <c r="F11" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G11" t="str">
         <v>First</v>
       </c>
       <c r="H11" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I11" t="str">
-        <v>Unpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="12">
@@ -734,16 +734,16 @@
         <v>UMaT/PG/0011/22</v>
       </c>
       <c r="B12" t="str">
-        <v>Kwaku Gyasi</v>
+        <v>Kofi Acheampong</v>
       </c>
       <c r="C12">
-        <v>5100</v>
+        <v>10300</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>10300</v>
       </c>
       <c r="E12">
-        <v>5100</v>
+        <v>0</v>
       </c>
       <c r="F12" t="str">
         <v>2025/2026</v>
@@ -752,10 +752,10 @@
         <v>Second</v>
       </c>
       <c r="H12" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I12" t="str">
-        <v>Unpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="13">
@@ -763,22 +763,22 @@
         <v>UMaT/PG/0012/22</v>
       </c>
       <c r="B13" t="str">
-        <v>Abena Boakye</v>
+        <v>Kwame Frimpong</v>
       </c>
       <c r="C13">
-        <v>5900</v>
+        <v>12000</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>5900</v>
+        <v>12000</v>
       </c>
       <c r="F13" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G13" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H13" t="str">
         <v>N/A</v>
@@ -792,19 +792,19 @@
         <v>UMaT/PG/0013/22</v>
       </c>
       <c r="B14" t="str">
-        <v>Ama Mensah</v>
+        <v>Kofi Mensah</v>
       </c>
       <c r="C14">
-        <v>8400</v>
+        <v>6600</v>
       </c>
       <c r="D14">
-        <v>8400</v>
+        <v>4000</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="F14" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G14" t="str">
         <v>First</v>
@@ -813,7 +813,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I14" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="15">
@@ -821,16 +821,16 @@
         <v>UMaT/PG/0014/22</v>
       </c>
       <c r="B15" t="str">
-        <v>Akosua Nkrumah</v>
+        <v>Mansa Agyemang</v>
       </c>
       <c r="C15">
-        <v>12800</v>
+        <v>12300</v>
       </c>
       <c r="D15">
-        <v>12800</v>
+        <v>11300</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F15" t="str">
         <v>2024/2025</v>
@@ -842,7 +842,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I15" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="16">
@@ -850,16 +850,16 @@
         <v>UMaT/PG/0015/22</v>
       </c>
       <c r="B16" t="str">
-        <v>Ekua Acheampong</v>
+        <v>Ebo Mensah</v>
       </c>
       <c r="C16">
-        <v>11500</v>
+        <v>7500</v>
       </c>
       <c r="D16">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="E16">
-        <v>8400</v>
+        <v>4300</v>
       </c>
       <c r="F16" t="str">
         <v>2023/2024</v>
@@ -879,28 +879,28 @@
         <v>UMaT/PG/0016/22</v>
       </c>
       <c r="B17" t="str">
-        <v>Kobina Owusu</v>
+        <v>Ato Frimpong</v>
       </c>
       <c r="C17">
-        <v>5000</v>
+        <v>5700</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="E17">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="F17" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G17" t="str">
         <v>Second</v>
       </c>
       <c r="H17" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I17" t="str">
-        <v>Unpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="18">
@@ -908,28 +908,28 @@
         <v>UMaT/PG/0017/22</v>
       </c>
       <c r="B18" t="str">
-        <v>Kakra Sarpong</v>
+        <v>Kwaku Opoku</v>
       </c>
       <c r="C18">
-        <v>11200</v>
+        <v>8400</v>
       </c>
       <c r="D18">
-        <v>11200</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>8400</v>
       </c>
       <c r="F18" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G18" t="str">
         <v>First</v>
       </c>
       <c r="H18" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I18" t="str">
-        <v>Paid</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="19">
@@ -937,22 +937,22 @@
         <v>UMaT/PG/0018/22</v>
       </c>
       <c r="B19" t="str">
-        <v>Akua Sarpong</v>
+        <v>Kwame Mensah</v>
       </c>
       <c r="C19">
-        <v>11000</v>
+        <v>8400</v>
       </c>
       <c r="D19">
-        <v>8600</v>
+        <v>5600</v>
       </c>
       <c r="E19">
-        <v>2400</v>
+        <v>2800</v>
       </c>
       <c r="F19" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G19" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H19" t="str">
         <v>Bank Transfer</v>
@@ -966,28 +966,28 @@
         <v>UMaT/PG/0019/22</v>
       </c>
       <c r="B20" t="str">
-        <v>Ato Darko</v>
+        <v>Afi Annan</v>
       </c>
       <c r="C20">
-        <v>10200</v>
+        <v>5700</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="E20">
-        <v>10200</v>
+        <v>0</v>
       </c>
       <c r="F20" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G20" t="str">
         <v>Second</v>
       </c>
       <c r="H20" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I20" t="str">
-        <v>Unpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="21">
@@ -995,28 +995,28 @@
         <v>UMaT/PG/0020/22</v>
       </c>
       <c r="B21" t="str">
-        <v>Kwabena Agyemang</v>
+        <v>Adwoa Darko</v>
       </c>
       <c r="C21">
-        <v>11200</v>
+        <v>7900</v>
       </c>
       <c r="D21">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>6200</v>
+        <v>7900</v>
       </c>
       <c r="F21" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G21" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H21" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I21" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="22">
@@ -1024,28 +1024,28 @@
         <v>UMaT/PG/0021/22</v>
       </c>
       <c r="B22" t="str">
-        <v>Ekua Afriyie</v>
+        <v>Afia Acheampong</v>
       </c>
       <c r="C22">
-        <v>8400</v>
+        <v>8700</v>
       </c>
       <c r="D22">
-        <v>9200</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>-800</v>
+        <v>8700</v>
       </c>
       <c r="F22" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G22" t="str">
         <v>First</v>
       </c>
       <c r="H22" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I22" t="str">
-        <v>Overpaid</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="23">
@@ -1053,22 +1053,22 @@
         <v>UMaT/PG/0022/22</v>
       </c>
       <c r="B23" t="str">
-        <v>Ebo Afriyie</v>
+        <v>Efua Annan</v>
       </c>
       <c r="C23">
-        <v>11600</v>
+        <v>7000</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>11600</v>
+        <v>7000</v>
       </c>
       <c r="F23" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G23" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H23" t="str">
         <v>N/A</v>
@@ -1082,22 +1082,22 @@
         <v>UMaT/PG/0023/22</v>
       </c>
       <c r="B24" t="str">
-        <v>Kodwo Ofori</v>
+        <v>Araba Nkrumah</v>
       </c>
       <c r="C24">
-        <v>8500</v>
+        <v>11700</v>
       </c>
       <c r="D24">
-        <v>8500</v>
+        <v>11700</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G24" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H24" t="str">
         <v>Bank Transfer</v>
@@ -1111,22 +1111,22 @@
         <v>UMaT/PG/0024/22</v>
       </c>
       <c r="B25" t="str">
-        <v>Ekua Addo</v>
+        <v>Ama Amoah</v>
       </c>
       <c r="C25">
-        <v>5300</v>
+        <v>9900</v>
       </c>
       <c r="D25">
-        <v>4900</v>
+        <v>3800</v>
       </c>
       <c r="E25">
-        <v>400</v>
+        <v>6100</v>
       </c>
       <c r="F25" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G25" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H25" t="str">
         <v>Bank Transfer</v>
@@ -1140,28 +1140,28 @@
         <v>UMaT/PG/0025/22</v>
       </c>
       <c r="B26" t="str">
-        <v>Araba Annan</v>
+        <v>Efua Akuffo</v>
       </c>
       <c r="C26">
-        <v>12600</v>
+        <v>6500</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="E26">
-        <v>12600</v>
+        <v>1500</v>
       </c>
       <c r="F26" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G26" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H26" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I26" t="str">
-        <v>Unpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="27">
@@ -1169,28 +1169,28 @@
         <v>UMaT/PG/0026/22</v>
       </c>
       <c r="B27" t="str">
-        <v>Kwame Boateng</v>
+        <v>Akosua Appiah</v>
       </c>
       <c r="C27">
-        <v>9500</v>
+        <v>6000</v>
       </c>
       <c r="D27">
-        <v>5400</v>
+        <v>6000</v>
       </c>
       <c r="E27">
-        <v>4100</v>
+        <v>0</v>
       </c>
       <c r="F27" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G27" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H27" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I27" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="28">
@@ -1198,28 +1198,28 @@
         <v>UMaT/PG/0027/22</v>
       </c>
       <c r="B28" t="str">
-        <v>Afia Mensah</v>
+        <v>Yaw Amoah</v>
       </c>
       <c r="C28">
-        <v>9800</v>
+        <v>11100</v>
       </c>
       <c r="D28">
-        <v>8500</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>1300</v>
+        <v>11100</v>
       </c>
       <c r="F28" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G28" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H28" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I28" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="29">
@@ -1227,28 +1227,28 @@
         <v>UMaT/PG/0028/22</v>
       </c>
       <c r="B29" t="str">
-        <v>Adjoa Mensah</v>
+        <v>Mensah Gyasi</v>
       </c>
       <c r="C29">
-        <v>9300</v>
+        <v>10000</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="E29">
-        <v>9300</v>
+        <v>0</v>
       </c>
       <c r="F29" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G29" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H29" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I29" t="str">
-        <v>Unpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="30">
@@ -1256,22 +1256,22 @@
         <v>UMaT/PG/0029/22</v>
       </c>
       <c r="B30" t="str">
-        <v>Abena Ansah</v>
+        <v>Afi Darko</v>
       </c>
       <c r="C30">
-        <v>10700</v>
+        <v>8700</v>
       </c>
       <c r="D30">
-        <v>10700</v>
+        <v>8700</v>
       </c>
       <c r="E30">
         <v>0</v>
       </c>
       <c r="F30" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G30" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H30" t="str">
         <v>Bank Transfer</v>
@@ -1285,19 +1285,19 @@
         <v>UMaT/PG/0030/22</v>
       </c>
       <c r="B31" t="str">
-        <v>Ekua Mensah</v>
+        <v>Afi Mensah</v>
       </c>
       <c r="C31">
-        <v>9400</v>
+        <v>12600</v>
       </c>
       <c r="D31">
-        <v>9400</v>
+        <v>12600</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
       <c r="F31" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G31" t="str">
         <v>Second</v>
@@ -1314,28 +1314,28 @@
         <v>UMaT/PG/0031/22</v>
       </c>
       <c r="B32" t="str">
-        <v>Kwabena Opoku</v>
+        <v>Abena Wiredu</v>
       </c>
       <c r="C32">
-        <v>6700</v>
+        <v>8400</v>
       </c>
       <c r="D32">
-        <v>6700</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>8400</v>
       </c>
       <c r="F32" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G32" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H32" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I32" t="str">
-        <v>Paid</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="33">
@@ -1343,28 +1343,28 @@
         <v>UMaT/PG/0032/22</v>
       </c>
       <c r="B33" t="str">
-        <v>Efua Annan</v>
+        <v>Yaa Osei</v>
       </c>
       <c r="C33">
-        <v>9300</v>
+        <v>9000</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="E33">
-        <v>9300</v>
+        <v>0</v>
       </c>
       <c r="F33" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G33" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H33" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I33" t="str">
-        <v>Unpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="34">
@@ -1372,28 +1372,28 @@
         <v>UMaT/PG/0033/22</v>
       </c>
       <c r="B34" t="str">
-        <v>Yaw Gyasi</v>
+        <v>Kwadwo Mensah</v>
       </c>
       <c r="C34">
-        <v>7400</v>
+        <v>6800</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="E34">
-        <v>7400</v>
+        <v>800</v>
       </c>
       <c r="F34" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G34" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H34" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I34" t="str">
-        <v>Unpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="35">
@@ -1401,28 +1401,28 @@
         <v>UMaT/PG/0034/22</v>
       </c>
       <c r="B35" t="str">
-        <v>Ebo Wiredu</v>
+        <v>Kwesi Addo</v>
       </c>
       <c r="C35">
-        <v>5700</v>
+        <v>8200</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="E35">
-        <v>5700</v>
+        <v>1200</v>
       </c>
       <c r="F35" t="str">
-        <v>2025/2026</v>
+        <v>2024/2025</v>
       </c>
       <c r="G35" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H35" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I35" t="str">
-        <v>Unpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="36">
@@ -1430,16 +1430,16 @@
         <v>UMaT/PG/0035/22</v>
       </c>
       <c r="B36" t="str">
-        <v>Esi Boateng</v>
+        <v>Kwame Annan</v>
       </c>
       <c r="C36">
-        <v>7600</v>
+        <v>12600</v>
       </c>
       <c r="D36">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>4900</v>
+        <v>12600</v>
       </c>
       <c r="F36" t="str">
         <v>2023/2024</v>
@@ -1448,10 +1448,10 @@
         <v>Second</v>
       </c>
       <c r="H36" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I36" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="37">
@@ -1459,28 +1459,28 @@
         <v>UMaT/PG/0036/22</v>
       </c>
       <c r="B37" t="str">
-        <v>Serwa Agyei</v>
+        <v>Ato Appiah</v>
       </c>
       <c r="C37">
-        <v>9700</v>
+        <v>6000</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="E37">
-        <v>9700</v>
+        <v>3200</v>
       </c>
       <c r="F37" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G37" t="str">
         <v>First</v>
       </c>
       <c r="H37" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I37" t="str">
-        <v>Unpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="38">
@@ -1488,22 +1488,22 @@
         <v>UMaT/PG/0037/22</v>
       </c>
       <c r="B38" t="str">
-        <v>Esi Addo</v>
+        <v>Araba Addo</v>
       </c>
       <c r="C38">
-        <v>5400</v>
+        <v>10200</v>
       </c>
       <c r="D38">
+        <v>5900</v>
+      </c>
+      <c r="E38">
         <v>4300</v>
       </c>
-      <c r="E38">
-        <v>1100</v>
-      </c>
       <c r="F38" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G38" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H38" t="str">
         <v>Bank Transfer</v>
@@ -1517,28 +1517,28 @@
         <v>UMaT/PG/0038/22</v>
       </c>
       <c r="B39" t="str">
-        <v>Panyin Addo</v>
+        <v>Serwa Darko</v>
       </c>
       <c r="C39">
-        <v>6900</v>
+        <v>7800</v>
       </c>
       <c r="D39">
-        <v>4300</v>
+        <v>7800</v>
       </c>
       <c r="E39">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="F39" t="str">
         <v>2023/2024</v>
       </c>
       <c r="G39" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H39" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I39" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="40">
@@ -1546,28 +1546,28 @@
         <v>UMaT/PG/0039/22</v>
       </c>
       <c r="B40" t="str">
-        <v>Ekua Ansah</v>
+        <v>Kwabena Agyei</v>
       </c>
       <c r="C40">
-        <v>11000</v>
+        <v>7500</v>
       </c>
       <c r="D40">
-        <v>11000</v>
+        <v>6700</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F40" t="str">
-        <v>2025/2026</v>
+        <v>2024/2025</v>
       </c>
       <c r="G40" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H40" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I40" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="41">
@@ -1575,22 +1575,22 @@
         <v>UMaT/PG/0040/22</v>
       </c>
       <c r="B41" t="str">
-        <v>Kofi Addo</v>
+        <v>Efua Amankwah</v>
       </c>
       <c r="C41">
-        <v>10200</v>
+        <v>9300</v>
       </c>
       <c r="D41">
-        <v>10200</v>
+        <v>9300</v>
       </c>
       <c r="E41">
         <v>0</v>
       </c>
       <c r="F41" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G41" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H41" t="str">
         <v>Bank Transfer</v>
@@ -1604,28 +1604,28 @@
         <v>UMaT/PG/0041/22</v>
       </c>
       <c r="B42" t="str">
-        <v>Kojo Boakye</v>
+        <v>Esi Danquah</v>
       </c>
       <c r="C42">
-        <v>6600</v>
+        <v>9300</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>9300</v>
       </c>
       <c r="E42">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="F42" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G42" t="str">
         <v>Second</v>
       </c>
       <c r="H42" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I42" t="str">
-        <v>Unpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="43">
@@ -1633,13 +1633,13 @@
         <v>UMaT/PG/0042/22</v>
       </c>
       <c r="B43" t="str">
-        <v>Adjoa Akuffo</v>
+        <v>Serwa Darko</v>
       </c>
       <c r="C43">
-        <v>11900</v>
+        <v>11700</v>
       </c>
       <c r="D43">
-        <v>11900</v>
+        <v>11700</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -1662,19 +1662,19 @@
         <v>UMaT/PG/0043/22</v>
       </c>
       <c r="B44" t="str">
-        <v>Afi Acheampong</v>
+        <v>Mansa Quaye</v>
       </c>
       <c r="C44">
-        <v>11800</v>
+        <v>5100</v>
       </c>
       <c r="D44">
-        <v>11800</v>
+        <v>3300</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="F44" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G44" t="str">
         <v>Second</v>
@@ -1683,7 +1683,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I44" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="45">
@@ -1691,22 +1691,22 @@
         <v>UMaT/PG/0044/22</v>
       </c>
       <c r="B45" t="str">
-        <v>Serwa Ofori</v>
+        <v>Araba Wiredu</v>
       </c>
       <c r="C45">
-        <v>10500</v>
+        <v>7200</v>
       </c>
       <c r="D45">
-        <v>6100</v>
+        <v>2000</v>
       </c>
       <c r="E45">
-        <v>4400</v>
+        <v>5200</v>
       </c>
       <c r="F45" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G45" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H45" t="str">
         <v>Bank Transfer</v>
@@ -1720,19 +1720,19 @@
         <v>UMaT/PG/0045/22</v>
       </c>
       <c r="B46" t="str">
-        <v>Araba Akuffo</v>
+        <v>Adwoa Quaye</v>
       </c>
       <c r="C46">
-        <v>10800</v>
+        <v>12900</v>
       </c>
       <c r="D46">
-        <v>12200</v>
+        <v>12900</v>
       </c>
       <c r="E46">
-        <v>-1400</v>
+        <v>0</v>
       </c>
       <c r="F46" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G46" t="str">
         <v>First</v>
@@ -1741,7 +1741,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I46" t="str">
-        <v>Overpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="47">
@@ -1749,16 +1749,16 @@
         <v>UMaT/PG/0046/22</v>
       </c>
       <c r="B47" t="str">
-        <v>Yaw Boakye</v>
+        <v>Araba Mensah</v>
       </c>
       <c r="C47">
-        <v>11200</v>
+        <v>12000</v>
       </c>
       <c r="D47">
-        <v>11200</v>
+        <v>0</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="F47" t="str">
         <v>2023/2024</v>
@@ -1767,10 +1767,10 @@
         <v>First</v>
       </c>
       <c r="H47" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I47" t="str">
-        <v>Paid</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="48">
@@ -1778,19 +1778,19 @@
         <v>UMaT/PG/0047/22</v>
       </c>
       <c r="B48" t="str">
-        <v>Panyin Addo</v>
+        <v>Mensah Asante</v>
       </c>
       <c r="C48">
-        <v>9500</v>
+        <v>11100</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>9500</v>
+        <v>11100</v>
       </c>
       <c r="F48" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G48" t="str">
         <v>Second</v>
@@ -1807,13 +1807,13 @@
         <v>UMaT/PG/0048/22</v>
       </c>
       <c r="B49" t="str">
-        <v>Araba Quaye</v>
+        <v>Mansa Darko</v>
       </c>
       <c r="C49">
-        <v>9400</v>
+        <v>5700</v>
       </c>
       <c r="D49">
-        <v>9400</v>
+        <v>5700</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -1822,7 +1822,7 @@
         <v>2025/2026</v>
       </c>
       <c r="G49" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H49" t="str">
         <v>Bank Transfer</v>
@@ -1836,28 +1836,28 @@
         <v>UMaT/PG/0049/22</v>
       </c>
       <c r="B50" t="str">
-        <v>Kwadwo Sarpong</v>
+        <v>Mansa Sarpong</v>
       </c>
       <c r="C50">
-        <v>5100</v>
+        <v>9900</v>
       </c>
       <c r="D50">
-        <v>5100</v>
+        <v>0</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>9900</v>
       </c>
       <c r="F50" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G50" t="str">
         <v>Second</v>
       </c>
       <c r="H50" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I50" t="str">
-        <v>Paid</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="51">
@@ -1865,28 +1865,28 @@
         <v>UMaT/PG/0050/22</v>
       </c>
       <c r="B51" t="str">
-        <v>Mensah Nkrumah</v>
+        <v>Panyin Adjei</v>
       </c>
       <c r="C51">
-        <v>6800</v>
+        <v>5100</v>
       </c>
       <c r="D51">
-        <v>6800</v>
+        <v>2600</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="F51" t="str">
         <v>2023/2024</v>
       </c>
       <c r="G51" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H51" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I51" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="52">
@@ -1894,19 +1894,19 @@
         <v>UMaT/PG/0051/22</v>
       </c>
       <c r="B52" t="str">
-        <v>Abena Nkrumah</v>
+        <v>Efua Asante</v>
       </c>
       <c r="C52">
-        <v>8200</v>
+        <v>11900</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>8200</v>
+        <v>11900</v>
       </c>
       <c r="F52" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G52" t="str">
         <v>Second</v>
@@ -1923,28 +1923,28 @@
         <v>UMaT/PG/0052/22</v>
       </c>
       <c r="B53" t="str">
-        <v>Yaa Frimpong</v>
+        <v>Efua Akuffo</v>
       </c>
       <c r="C53">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="E53">
-        <v>12000</v>
+        <v>8500</v>
       </c>
       <c r="F53" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G53" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H53" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I53" t="str">
-        <v>Unpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="54">
@@ -1952,19 +1952,19 @@
         <v>UMaT/PG/0053/22</v>
       </c>
       <c r="B54" t="str">
-        <v>Kwesi Quaye</v>
+        <v>Mansa Mensah</v>
       </c>
       <c r="C54">
-        <v>11900</v>
+        <v>11300</v>
       </c>
       <c r="D54">
-        <v>11900</v>
+        <v>11300</v>
       </c>
       <c r="E54">
         <v>0</v>
       </c>
       <c r="F54" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G54" t="str">
         <v>Second</v>
@@ -1981,19 +1981,19 @@
         <v>UMaT/PG/0054/22</v>
       </c>
       <c r="B55" t="str">
-        <v>Kojo Annan</v>
+        <v>Adwoa Owusu</v>
       </c>
       <c r="C55">
-        <v>10200</v>
+        <v>12300</v>
       </c>
       <c r="D55">
-        <v>10200</v>
+        <v>12300</v>
       </c>
       <c r="E55">
         <v>0</v>
       </c>
       <c r="F55" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G55" t="str">
         <v>Second</v>
@@ -2010,16 +2010,16 @@
         <v>UMaT/PG/0055/22</v>
       </c>
       <c r="B56" t="str">
-        <v>Afi Acheampong</v>
+        <v>Ekua Mensah</v>
       </c>
       <c r="C56">
-        <v>11300</v>
+        <v>5100</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="E56">
-        <v>11300</v>
+        <v>0</v>
       </c>
       <c r="F56" t="str">
         <v>2023/2024</v>
@@ -2028,10 +2028,10 @@
         <v>First</v>
       </c>
       <c r="H56" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I56" t="str">
-        <v>Unpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="57">
@@ -2039,19 +2039,19 @@
         <v>UMaT/PG/0056/22</v>
       </c>
       <c r="B57" t="str">
-        <v>Kofi Ofori</v>
+        <v>Kojo Wiredu</v>
       </c>
       <c r="C57">
-        <v>9900</v>
+        <v>6400</v>
       </c>
       <c r="D57">
-        <v>9900</v>
+        <v>6400</v>
       </c>
       <c r="E57">
         <v>0</v>
       </c>
       <c r="F57" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G57" t="str">
         <v>Second</v>
@@ -2068,22 +2068,22 @@
         <v>UMaT/PG/0057/22</v>
       </c>
       <c r="B58" t="str">
-        <v>Kodwo Agyei</v>
+        <v>Kwaku Annan</v>
       </c>
       <c r="C58">
-        <v>7000</v>
+        <v>9700</v>
       </c>
       <c r="D58">
-        <v>2700</v>
+        <v>9100</v>
       </c>
       <c r="E58">
-        <v>4300</v>
+        <v>600</v>
       </c>
       <c r="F58" t="str">
         <v>2024/2025</v>
       </c>
       <c r="G58" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H58" t="str">
         <v>Bank Transfer</v>
@@ -2097,28 +2097,28 @@
         <v>UMaT/PG/0058/22</v>
       </c>
       <c r="B59" t="str">
-        <v>Yaw Owusu</v>
+        <v>Mensah Appiah</v>
       </c>
       <c r="C59">
-        <v>10500</v>
+        <v>5800</v>
       </c>
       <c r="D59">
-        <v>10500</v>
+        <v>0</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="F59" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G59" t="str">
         <v>Second</v>
       </c>
       <c r="H59" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I59" t="str">
-        <v>Paid</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="60">
@@ -2126,13 +2126,13 @@
         <v>UMaT/PG/0059/22</v>
       </c>
       <c r="B60" t="str">
-        <v>Kwadwo Addo</v>
+        <v>Mansa Sarpong</v>
       </c>
       <c r="C60">
-        <v>9600</v>
+        <v>8200</v>
       </c>
       <c r="D60">
-        <v>9600</v>
+        <v>8200</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -2141,7 +2141,7 @@
         <v>2025/2026</v>
       </c>
       <c r="G60" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H60" t="str">
         <v>Bank Transfer</v>
@@ -2155,19 +2155,19 @@
         <v>UMaT/PG/0060/22</v>
       </c>
       <c r="B61" t="str">
-        <v>Ama Opoku</v>
+        <v>Kwesi Appiah</v>
       </c>
       <c r="C61">
-        <v>6900</v>
+        <v>12500</v>
       </c>
       <c r="D61">
-        <v>6900</v>
+        <v>12500</v>
       </c>
       <c r="E61">
         <v>0</v>
       </c>
       <c r="F61" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G61" t="str">
         <v>Second</v>
@@ -2184,19 +2184,19 @@
         <v>UMaT/PG/0061/22</v>
       </c>
       <c r="B62" t="str">
-        <v>Adjoa Wiredu</v>
+        <v>Kobina Mensah</v>
       </c>
       <c r="C62">
-        <v>8400</v>
+        <v>8700</v>
       </c>
       <c r="D62">
-        <v>7100</v>
+        <v>8700</v>
       </c>
       <c r="E62">
-        <v>1300</v>
+        <v>0</v>
       </c>
       <c r="F62" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G62" t="str">
         <v>First</v>
@@ -2205,7 +2205,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I62" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="63">
@@ -2213,16 +2213,16 @@
         <v>UMaT/PG/0062/22</v>
       </c>
       <c r="B63" t="str">
-        <v>Kojo Danquah</v>
+        <v>Akosua Wiredu</v>
       </c>
       <c r="C63">
-        <v>11000</v>
+        <v>10200</v>
       </c>
       <c r="D63">
-        <v>11000</v>
+        <v>8600</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="F63" t="str">
         <v>2023/2024</v>
@@ -2234,7 +2234,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I63" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="64">
@@ -2242,16 +2242,16 @@
         <v>UMaT/PG/0063/22</v>
       </c>
       <c r="B64" t="str">
-        <v>Kwame Gyasi</v>
+        <v>Panyin Owusu</v>
       </c>
       <c r="C64">
-        <v>8500</v>
+        <v>9800</v>
       </c>
       <c r="D64">
-        <v>8500</v>
+        <v>11600</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>-1800</v>
       </c>
       <c r="F64" t="str">
         <v>2024/2025</v>
@@ -2263,7 +2263,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I64" t="str">
-        <v>Paid</v>
+        <v>Overpaid</v>
       </c>
     </row>
     <row r="65">
@@ -2271,19 +2271,19 @@
         <v>UMaT/PG/0064/22</v>
       </c>
       <c r="B65" t="str">
-        <v>Abena Mensah</v>
+        <v>Akua Danquah</v>
       </c>
       <c r="C65">
-        <v>9500</v>
+        <v>11400</v>
       </c>
       <c r="D65">
-        <v>9500</v>
+        <v>11400</v>
       </c>
       <c r="E65">
         <v>0</v>
       </c>
       <c r="F65" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G65" t="str">
         <v>First</v>
@@ -2300,28 +2300,28 @@
         <v>UMaT/PG/0065/22</v>
       </c>
       <c r="B66" t="str">
-        <v>Kobina Sarpong</v>
+        <v>Adjoa Opoku</v>
       </c>
       <c r="C66">
-        <v>9700</v>
+        <v>10200</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="E66">
-        <v>9700</v>
+        <v>0</v>
       </c>
       <c r="F66" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G66" t="str">
         <v>First</v>
       </c>
       <c r="H66" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I66" t="str">
-        <v>Unpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="67">
@@ -2329,28 +2329,28 @@
         <v>UMaT/PG/0066/22</v>
       </c>
       <c r="B67" t="str">
-        <v>Kobina Ansah</v>
+        <v>Mansa Boateng</v>
       </c>
       <c r="C67">
-        <v>5100</v>
+        <v>12400</v>
       </c>
       <c r="D67">
-        <v>1800</v>
+        <v>12400</v>
       </c>
       <c r="E67">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="F67" t="str">
         <v>2025/2026</v>
       </c>
       <c r="G67" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H67" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I67" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="68">
@@ -2358,28 +2358,28 @@
         <v>UMaT/PG/0067/22</v>
       </c>
       <c r="B68" t="str">
-        <v>Kwadwo Darko</v>
+        <v>Ato Owusu</v>
       </c>
       <c r="C68">
-        <v>6800</v>
+        <v>11400</v>
       </c>
       <c r="D68">
-        <v>6800</v>
+        <v>3600</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="F68" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G68" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H68" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I68" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="69">
@@ -2387,28 +2387,28 @@
         <v>UMaT/PG/0068/22</v>
       </c>
       <c r="B69" t="str">
-        <v>Mansa Gyasi</v>
+        <v>Kwame Agyemang</v>
       </c>
       <c r="C69">
-        <v>7700</v>
+        <v>10400</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>10400</v>
       </c>
       <c r="E69">
-        <v>7700</v>
+        <v>0</v>
       </c>
       <c r="F69" t="str">
         <v>2025/2026</v>
       </c>
       <c r="G69" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H69" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I69" t="str">
-        <v>Unpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="70">
@@ -2416,19 +2416,19 @@
         <v>UMaT/PG/0069/22</v>
       </c>
       <c r="B70" t="str">
-        <v>Ebo Opoku</v>
+        <v>Kwaku Ofori</v>
       </c>
       <c r="C70">
-        <v>7300</v>
+        <v>9300</v>
       </c>
       <c r="D70">
-        <v>3900</v>
+        <v>9300</v>
       </c>
       <c r="E70">
-        <v>3400</v>
+        <v>0</v>
       </c>
       <c r="F70" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G70" t="str">
         <v>Second</v>
@@ -2437,7 +2437,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I70" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="71">
@@ -2445,19 +2445,19 @@
         <v>UMaT/PG/0070/22</v>
       </c>
       <c r="B71" t="str">
-        <v>Yaa Sarpong</v>
+        <v>Abena Ansah</v>
       </c>
       <c r="C71">
-        <v>13000</v>
+        <v>5800</v>
       </c>
       <c r="D71">
-        <v>3500</v>
+        <v>2600</v>
       </c>
       <c r="E71">
-        <v>9500</v>
+        <v>3200</v>
       </c>
       <c r="F71" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G71" t="str">
         <v>First</v>
@@ -2474,28 +2474,28 @@
         <v>UMaT/PG/0071/22</v>
       </c>
       <c r="B72" t="str">
-        <v>Akosua Wiredu</v>
+        <v>Yaw Gyasi</v>
       </c>
       <c r="C72">
-        <v>5700</v>
+        <v>8900</v>
       </c>
       <c r="D72">
-        <v>6200</v>
+        <v>8900</v>
       </c>
       <c r="E72">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="F72" t="str">
-        <v>2025/2026</v>
+        <v>2024/2025</v>
       </c>
       <c r="G72" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H72" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I72" t="str">
-        <v>Overpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="73">
@@ -2503,28 +2503,28 @@
         <v>UMaT/PG/0072/22</v>
       </c>
       <c r="B73" t="str">
-        <v>Akosua Ofori</v>
+        <v>Araba Quaye</v>
       </c>
       <c r="C73">
-        <v>8900</v>
+        <v>13000</v>
       </c>
       <c r="D73">
-        <v>8900</v>
+        <v>11900</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="F73" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G73" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H73" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I73" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="74">
@@ -2532,28 +2532,28 @@
         <v>UMaT/PG/0073/22</v>
       </c>
       <c r="B74" t="str">
-        <v>Afi Akuffo</v>
+        <v>Kofi Danquah</v>
       </c>
       <c r="C74">
-        <v>8800</v>
+        <v>10800</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="E74">
-        <v>8800</v>
+        <v>2700</v>
       </c>
       <c r="F74" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G74" t="str">
         <v>Second</v>
       </c>
       <c r="H74" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I74" t="str">
-        <v>Unpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="75">
@@ -2561,28 +2561,28 @@
         <v>UMaT/PG/0074/22</v>
       </c>
       <c r="B75" t="str">
-        <v>Kwaku Danquah</v>
+        <v>Araba Agyei</v>
       </c>
       <c r="C75">
-        <v>5100</v>
+        <v>6300</v>
       </c>
       <c r="D75">
-        <v>5100</v>
+        <v>0</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="F75" t="str">
         <v>2025/2026</v>
       </c>
       <c r="G75" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H75" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I75" t="str">
-        <v>Paid</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="76">
@@ -2590,28 +2590,28 @@
         <v>UMaT/PG/0075/22</v>
       </c>
       <c r="B76" t="str">
-        <v>Akua Mensah</v>
+        <v>Kwaku Owusu</v>
       </c>
       <c r="C76">
-        <v>12000</v>
+        <v>11400</v>
       </c>
       <c r="D76">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>11400</v>
       </c>
       <c r="F76" t="str">
         <v>2025/2026</v>
       </c>
       <c r="G76" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H76" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I76" t="str">
-        <v>Paid</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="77">
@@ -2619,28 +2619,28 @@
         <v>UMaT/PG/0076/24</v>
       </c>
       <c r="B77" t="str">
-        <v>Ama Annan</v>
+        <v>Efua Ofori</v>
       </c>
       <c r="C77">
-        <v>10000</v>
+        <v>6800</v>
       </c>
       <c r="D77">
-        <v>4800</v>
+        <v>6800</v>
       </c>
       <c r="E77">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="F77" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G77" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H77" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I77" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="78">
@@ -2648,28 +2648,28 @@
         <v>UMaT/PG/0077/24</v>
       </c>
       <c r="B78" t="str">
-        <v>Ama Agyemang</v>
+        <v>Kwame Gyasi</v>
       </c>
       <c r="C78">
-        <v>7500</v>
+        <v>12900</v>
       </c>
       <c r="D78">
-        <v>7500</v>
+        <v>0</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>12900</v>
       </c>
       <c r="F78" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G78" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H78" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I78" t="str">
-        <v>Paid</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="79">
@@ -2677,28 +2677,28 @@
         <v>UMaT/PG/0078/24</v>
       </c>
       <c r="B79" t="str">
-        <v>Akua Addo</v>
+        <v>Mansa Sarpong</v>
       </c>
       <c r="C79">
-        <v>8900</v>
+        <v>8700</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>9400</v>
       </c>
       <c r="E79">
-        <v>8900</v>
+        <v>-700</v>
       </c>
       <c r="F79" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G79" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H79" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I79" t="str">
-        <v>Unpaid</v>
+        <v>Overpaid</v>
       </c>
     </row>
     <row r="80">
@@ -2706,28 +2706,28 @@
         <v>UMaT/PG/0079/24</v>
       </c>
       <c r="B80" t="str">
-        <v>Efua Frimpong</v>
+        <v>Ama Agyei</v>
       </c>
       <c r="C80">
-        <v>10300</v>
+        <v>5200</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="E80">
-        <v>10300</v>
+        <v>0</v>
       </c>
       <c r="F80" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G80" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H80" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I80" t="str">
-        <v>Unpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="81">
@@ -2735,19 +2735,19 @@
         <v>UMaT/PG/0080/24</v>
       </c>
       <c r="B81" t="str">
-        <v>Mansa Quaye</v>
+        <v>Kwadwo Annan</v>
       </c>
       <c r="C81">
-        <v>7600</v>
+        <v>6100</v>
       </c>
       <c r="D81">
-        <v>7600</v>
+        <v>6100</v>
       </c>
       <c r="E81">
         <v>0</v>
       </c>
       <c r="F81" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G81" t="str">
         <v>Second</v>
@@ -2764,28 +2764,28 @@
         <v>UMaT/PG/0081/24</v>
       </c>
       <c r="B82" t="str">
-        <v>Kofi Sarpong</v>
+        <v>Kwabena Nkrumah</v>
       </c>
       <c r="C82">
-        <v>9000</v>
+        <v>8800</v>
       </c>
       <c r="D82">
-        <v>9500</v>
+        <v>8800</v>
       </c>
       <c r="E82">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="F82" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G82" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H82" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I82" t="str">
-        <v>Overpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="83">
@@ -2793,22 +2793,22 @@
         <v>UMaT/PG/0082/24</v>
       </c>
       <c r="B83" t="str">
-        <v>Afi Boakye</v>
+        <v>Ebo Addo</v>
       </c>
       <c r="C83">
-        <v>6300</v>
+        <v>7300</v>
       </c>
       <c r="D83">
         <v>0</v>
       </c>
       <c r="E83">
-        <v>6300</v>
+        <v>7300</v>
       </c>
       <c r="F83" t="str">
         <v>2023/2024</v>
       </c>
       <c r="G83" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H83" t="str">
         <v>N/A</v>
@@ -2822,13 +2822,13 @@
         <v>UMaT/PG/0083/24</v>
       </c>
       <c r="B84" t="str">
-        <v>Abena Frimpong</v>
+        <v>Yaa Frimpong</v>
       </c>
       <c r="C84">
-        <v>6200</v>
+        <v>5300</v>
       </c>
       <c r="D84">
-        <v>6200</v>
+        <v>5300</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>2023/2024</v>
       </c>
       <c r="G84" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H84" t="str">
         <v>Bank Transfer</v>
@@ -2851,28 +2851,28 @@
         <v>UMaT/PG/0084/24</v>
       </c>
       <c r="B85" t="str">
-        <v>Kofi Appiah</v>
+        <v>Kojo Mensah</v>
       </c>
       <c r="C85">
-        <v>6400</v>
+        <v>5400</v>
       </c>
       <c r="D85">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="E85">
-        <v>1900</v>
+        <v>5400</v>
       </c>
       <c r="F85" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G85" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H85" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I85" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="86">
@@ -2880,16 +2880,16 @@
         <v>UMaT/PG/0085/24</v>
       </c>
       <c r="B86" t="str">
-        <v>Ato Ansah</v>
+        <v>Ebo Boateng</v>
       </c>
       <c r="C86">
-        <v>7700</v>
+        <v>12000</v>
       </c>
       <c r="D86">
-        <v>7700</v>
+        <v>4000</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="F86" t="str">
         <v>2025/2026</v>
@@ -2901,7 +2901,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I86" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="87">
@@ -2909,28 +2909,28 @@
         <v>UMaT/PG/0086/24</v>
       </c>
       <c r="B87" t="str">
-        <v>Afia Boateng</v>
+        <v>Kofi Boakye</v>
       </c>
       <c r="C87">
-        <v>7600</v>
+        <v>12800</v>
       </c>
       <c r="D87">
-        <v>8500</v>
+        <v>12800</v>
       </c>
       <c r="E87">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="F87" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G87" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H87" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I87" t="str">
-        <v>Overpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="88">
@@ -2938,28 +2938,28 @@
         <v>UMaT/PG/0087/24</v>
       </c>
       <c r="B88" t="str">
-        <v>Kobina Darko</v>
+        <v>Araba Acheampong</v>
       </c>
       <c r="C88">
-        <v>6700</v>
+        <v>10800</v>
       </c>
       <c r="D88">
-        <v>6700</v>
+        <v>0</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="F88" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G88" t="str">
         <v>Second</v>
       </c>
       <c r="H88" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I88" t="str">
-        <v>Paid</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="89">
@@ -2967,22 +2967,22 @@
         <v>UMaT/PG/0088/24</v>
       </c>
       <c r="B89" t="str">
-        <v>Abena Quaye</v>
+        <v>Kwaku Wiredu</v>
       </c>
       <c r="C89">
-        <v>7700</v>
+        <v>7100</v>
       </c>
       <c r="D89">
-        <v>7700</v>
+        <v>7100</v>
       </c>
       <c r="E89">
         <v>0</v>
       </c>
       <c r="F89" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G89" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H89" t="str">
         <v>Bank Transfer</v>
@@ -2996,19 +2996,19 @@
         <v>UMaT/PG/0089/24</v>
       </c>
       <c r="B90" t="str">
-        <v>Akua Wiredu</v>
+        <v>Kakra Mensah</v>
       </c>
       <c r="C90">
-        <v>9500</v>
+        <v>12600</v>
       </c>
       <c r="D90">
-        <v>10200</v>
+        <v>4500</v>
       </c>
       <c r="E90">
-        <v>-700</v>
+        <v>8100</v>
       </c>
       <c r="F90" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G90" t="str">
         <v>First</v>
@@ -3017,7 +3017,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I90" t="str">
-        <v>Overpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="91">
@@ -3025,28 +3025,28 @@
         <v>UMaT/PG/0090/24</v>
       </c>
       <c r="B91" t="str">
-        <v>Efua Agyei</v>
+        <v>Kwabena Afriyie</v>
       </c>
       <c r="C91">
-        <v>9300</v>
+        <v>11900</v>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="E91">
-        <v>9300</v>
+        <v>7700</v>
       </c>
       <c r="F91" t="str">
         <v>2023/2024</v>
       </c>
       <c r="G91" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H91" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I91" t="str">
-        <v>Unpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="92">
@@ -3054,19 +3054,19 @@
         <v>UMaT/PG/0091/24</v>
       </c>
       <c r="B92" t="str">
-        <v>Esi Adjei</v>
+        <v>Yaa Yeboah</v>
       </c>
       <c r="C92">
-        <v>10200</v>
+        <v>10300</v>
       </c>
       <c r="D92">
-        <v>8900</v>
+        <v>8600</v>
       </c>
       <c r="E92">
-        <v>1300</v>
+        <v>1700</v>
       </c>
       <c r="F92" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G92" t="str">
         <v>Second</v>
@@ -3083,16 +3083,16 @@
         <v>UMaT/PG/0092/24</v>
       </c>
       <c r="B93" t="str">
-        <v>Ebo Acheampong</v>
+        <v>Kojo Sarpong</v>
       </c>
       <c r="C93">
-        <v>12800</v>
+        <v>12300</v>
       </c>
       <c r="D93">
-        <v>12800</v>
+        <v>0</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>12300</v>
       </c>
       <c r="F93" t="str">
         <v>2024/2025</v>
@@ -3101,10 +3101,10 @@
         <v>Second</v>
       </c>
       <c r="H93" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I93" t="str">
-        <v>Paid</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="94">
@@ -3112,28 +3112,28 @@
         <v>UMaT/PG/0093/24</v>
       </c>
       <c r="B94" t="str">
-        <v>Yaw Nkrumah</v>
+        <v>Kojo Afriyie</v>
       </c>
       <c r="C94">
-        <v>7800</v>
+        <v>11400</v>
       </c>
       <c r="D94">
-        <v>8700</v>
+        <v>11400</v>
       </c>
       <c r="E94">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="F94" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G94" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H94" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I94" t="str">
-        <v>Overpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="95">
@@ -3141,28 +3141,28 @@
         <v>UMaT/PG/0094/24</v>
       </c>
       <c r="B95" t="str">
-        <v>Kobina Boateng</v>
+        <v>Ato Amoah</v>
       </c>
       <c r="C95">
-        <v>7400</v>
+        <v>10900</v>
       </c>
       <c r="D95">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="E95">
-        <v>1400</v>
+        <v>10900</v>
       </c>
       <c r="F95" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G95" t="str">
         <v>Second</v>
       </c>
       <c r="H95" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I95" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="96">
@@ -3170,16 +3170,16 @@
         <v>UMaT/PG/0095/24</v>
       </c>
       <c r="B96" t="str">
-        <v>Mensah Asante</v>
+        <v>Kodwo Frimpong</v>
       </c>
       <c r="C96">
-        <v>8000</v>
+        <v>6100</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="E96">
-        <v>8000</v>
+        <v>4200</v>
       </c>
       <c r="F96" t="str">
         <v>2023/2024</v>
@@ -3188,10 +3188,10 @@
         <v>Second</v>
       </c>
       <c r="H96" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I96" t="str">
-        <v>Unpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="97">
@@ -3199,16 +3199,16 @@
         <v>UMaT/PG/0096/24</v>
       </c>
       <c r="B97" t="str">
-        <v>Araba Sarpong</v>
+        <v>Abena Darko</v>
       </c>
       <c r="C97">
-        <v>7000</v>
+        <v>10200</v>
       </c>
       <c r="D97">
-        <v>5200</v>
+        <v>3900</v>
       </c>
       <c r="E97">
-        <v>1800</v>
+        <v>6300</v>
       </c>
       <c r="F97" t="str">
         <v>2023/2024</v>
@@ -3228,28 +3228,28 @@
         <v>UMaT/PG/0097/24</v>
       </c>
       <c r="B98" t="str">
-        <v>Kwame Gyasi</v>
+        <v>Serwa Ofori</v>
       </c>
       <c r="C98">
-        <v>10300</v>
+        <v>6800</v>
       </c>
       <c r="D98">
-        <v>8200</v>
+        <v>0</v>
       </c>
       <c r="E98">
-        <v>2100</v>
+        <v>6800</v>
       </c>
       <c r="F98" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G98" t="str">
         <v>First</v>
       </c>
       <c r="H98" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I98" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="99">
@@ -3257,28 +3257,28 @@
         <v>UMaT/PG/0098/24</v>
       </c>
       <c r="B99" t="str">
-        <v>Kwabena Adjei</v>
+        <v>Kojo Adjei</v>
       </c>
       <c r="C99">
-        <v>8200</v>
+        <v>9900</v>
       </c>
       <c r="D99">
-        <v>3600</v>
+        <v>11300</v>
       </c>
       <c r="E99">
-        <v>4600</v>
+        <v>-1400</v>
       </c>
       <c r="F99" t="str">
-        <v>2025/2026</v>
+        <v>2024/2025</v>
       </c>
       <c r="G99" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H99" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I99" t="str">
-        <v>Partial</v>
+        <v>Overpaid</v>
       </c>
     </row>
     <row r="100">
@@ -3286,28 +3286,28 @@
         <v>UMaT/PG/0099/24</v>
       </c>
       <c r="B100" t="str">
-        <v>Ebo Akuffo</v>
+        <v>Efua Darko</v>
       </c>
       <c r="C100">
-        <v>9700</v>
+        <v>5200</v>
       </c>
       <c r="D100">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="E100">
-        <v>9700</v>
+        <v>600</v>
       </c>
       <c r="F100" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G100" t="str">
         <v>First</v>
       </c>
       <c r="H100" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I100" t="str">
-        <v>Unpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="101">
@@ -3315,28 +3315,28 @@
         <v>UMaT/PG/0100/24</v>
       </c>
       <c r="B101" t="str">
-        <v>Araba Darko</v>
+        <v>Kwabena Acheampong</v>
       </c>
       <c r="C101">
-        <v>11100</v>
+        <v>9400</v>
       </c>
       <c r="D101">
-        <v>11100</v>
+        <v>10300</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="F101" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G101" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H101" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I101" t="str">
-        <v>Paid</v>
+        <v>Overpaid</v>
       </c>
     </row>
     <row r="102">
@@ -3344,19 +3344,19 @@
         <v>UMaT/PG/0101/24</v>
       </c>
       <c r="B102" t="str">
-        <v>Kojo Wiredu</v>
+        <v>Mansa Sarpong</v>
       </c>
       <c r="C102">
-        <v>8700</v>
+        <v>6500</v>
       </c>
       <c r="D102">
-        <v>6500</v>
+        <v>4700</v>
       </c>
       <c r="E102">
-        <v>2200</v>
+        <v>1800</v>
       </c>
       <c r="F102" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G102" t="str">
         <v>Second</v>
@@ -3373,28 +3373,28 @@
         <v>UMaT/PG/0102/24</v>
       </c>
       <c r="B103" t="str">
-        <v>Yaw Darko</v>
+        <v>Adwoa Annan</v>
       </c>
       <c r="C103">
-        <v>6000</v>
+        <v>9500</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>11300</v>
       </c>
       <c r="E103">
-        <v>6000</v>
+        <v>-1800</v>
       </c>
       <c r="F103" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G103" t="str">
         <v>First</v>
       </c>
       <c r="H103" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I103" t="str">
-        <v>Unpaid</v>
+        <v>Overpaid</v>
       </c>
     </row>
     <row r="104">
@@ -3402,16 +3402,16 @@
         <v>UMaT/PG/0103/24</v>
       </c>
       <c r="B104" t="str">
-        <v>Kobina Gyasi</v>
+        <v>Adjoa Adjei</v>
       </c>
       <c r="C104">
-        <v>12200</v>
+        <v>7900</v>
       </c>
       <c r="D104">
-        <v>6900</v>
+        <v>7900</v>
       </c>
       <c r="E104">
-        <v>5300</v>
+        <v>0</v>
       </c>
       <c r="F104" t="str">
         <v>2023/2024</v>
@@ -3423,7 +3423,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I104" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="105">
@@ -3431,19 +3431,19 @@
         <v>UMaT/PG/0104/24</v>
       </c>
       <c r="B105" t="str">
-        <v>Ebo Wiredu</v>
+        <v>Akosua Amankwah</v>
       </c>
       <c r="C105">
-        <v>6500</v>
+        <v>12000</v>
       </c>
       <c r="D105">
-        <v>6500</v>
+        <v>7500</v>
       </c>
       <c r="E105">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="F105" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G105" t="str">
         <v>First</v>
@@ -3452,7 +3452,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I105" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="106">
@@ -3460,16 +3460,16 @@
         <v>UMaT/PG/0105/24</v>
       </c>
       <c r="B106" t="str">
-        <v>Mansa Darko</v>
+        <v>Akua Boateng</v>
       </c>
       <c r="C106">
-        <v>7100</v>
+        <v>6600</v>
       </c>
       <c r="D106">
-        <v>7100</v>
+        <v>5900</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F106" t="str">
         <v>2024/2025</v>
@@ -3481,7 +3481,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I106" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="107">
@@ -3489,28 +3489,28 @@
         <v>UMaT/PG/0106/24</v>
       </c>
       <c r="B107" t="str">
-        <v>Afi Boateng</v>
+        <v>Serwa Agyei</v>
       </c>
       <c r="C107">
-        <v>11600</v>
+        <v>12700</v>
       </c>
       <c r="D107">
-        <v>5300</v>
+        <v>0</v>
       </c>
       <c r="E107">
-        <v>6300</v>
+        <v>12700</v>
       </c>
       <c r="F107" t="str">
-        <v>2025/2026</v>
+        <v>2024/2025</v>
       </c>
       <c r="G107" t="str">
         <v>First</v>
       </c>
       <c r="H107" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I107" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="108">
@@ -3518,28 +3518,28 @@
         <v>UMaT/PG/0107/24</v>
       </c>
       <c r="B108" t="str">
-        <v>Kwadwo Sarpong</v>
+        <v>Efua Appiah</v>
       </c>
       <c r="C108">
-        <v>5800</v>
+        <v>5100</v>
       </c>
       <c r="D108">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="E108">
-        <v>3400</v>
+        <v>5100</v>
       </c>
       <c r="F108" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G108" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H108" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I108" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="109">
@@ -3547,16 +3547,16 @@
         <v>UMaT/PG/0108/24</v>
       </c>
       <c r="B109" t="str">
-        <v>Esi Annan</v>
+        <v>Kofi Wiredu</v>
       </c>
       <c r="C109">
-        <v>5500</v>
+        <v>12800</v>
       </c>
       <c r="D109">
-        <v>5500</v>
+        <v>0</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>12800</v>
       </c>
       <c r="F109" t="str">
         <v>2024/2025</v>
@@ -3565,10 +3565,10 @@
         <v>Second</v>
       </c>
       <c r="H109" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I109" t="str">
-        <v>Paid</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="110">
@@ -3576,28 +3576,28 @@
         <v>UMaT/PG/0109/24</v>
       </c>
       <c r="B110" t="str">
-        <v>Abena Ansah</v>
+        <v>Akua Wiredu</v>
       </c>
       <c r="C110">
-        <v>7400</v>
+        <v>9600</v>
       </c>
       <c r="D110">
-        <v>7400</v>
+        <v>3900</v>
       </c>
       <c r="E110">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="F110" t="str">
         <v>2024/2025</v>
       </c>
       <c r="G110" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H110" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I110" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="111">
@@ -3605,28 +3605,28 @@
         <v>UMaT/PG/0110/24</v>
       </c>
       <c r="B111" t="str">
-        <v>Afia Acheampong</v>
+        <v>Kwadwo Acheampong</v>
       </c>
       <c r="C111">
-        <v>12200</v>
+        <v>12800</v>
       </c>
       <c r="D111">
-        <v>10700</v>
+        <v>0</v>
       </c>
       <c r="E111">
-        <v>1500</v>
+        <v>12800</v>
       </c>
       <c r="F111" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G111" t="str">
         <v>Second</v>
       </c>
       <c r="H111" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I111" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="112">
@@ -3634,22 +3634,22 @@
         <v>UMaT/PG/0111/24</v>
       </c>
       <c r="B112" t="str">
-        <v>Kwaku Opoku</v>
+        <v>Adwoa Owusu</v>
       </c>
       <c r="C112">
-        <v>7800</v>
+        <v>9000</v>
       </c>
       <c r="D112">
-        <v>4400</v>
+        <v>2600</v>
       </c>
       <c r="E112">
-        <v>3400</v>
+        <v>6400</v>
       </c>
       <c r="F112" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G112" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H112" t="str">
         <v>Bank Transfer</v>
@@ -3663,22 +3663,22 @@
         <v>UMaT/PG/0112/24</v>
       </c>
       <c r="B113" t="str">
-        <v>Efua Danquah</v>
+        <v>Kwesi Amoah</v>
       </c>
       <c r="C113">
-        <v>8800</v>
+        <v>9700</v>
       </c>
       <c r="D113">
-        <v>3500</v>
+        <v>8000</v>
       </c>
       <c r="E113">
-        <v>5300</v>
+        <v>1700</v>
       </c>
       <c r="F113" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G113" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H113" t="str">
         <v>Bank Transfer</v>
@@ -3692,28 +3692,28 @@
         <v>UMaT/PG/0113/24</v>
       </c>
       <c r="B114" t="str">
-        <v>Afia Frimpong</v>
+        <v>Kwabena Addo</v>
       </c>
       <c r="C114">
-        <v>11300</v>
+        <v>10000</v>
       </c>
       <c r="D114">
-        <v>3100</v>
+        <v>10000</v>
       </c>
       <c r="E114">
-        <v>8200</v>
+        <v>0</v>
       </c>
       <c r="F114" t="str">
         <v>2024/2025</v>
       </c>
       <c r="G114" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H114" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I114" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="115">
@@ -3721,19 +3721,19 @@
         <v>UMaT/PG/0114/24</v>
       </c>
       <c r="B115" t="str">
-        <v>Kwadwo Boakye</v>
+        <v>Kofi Amankwah</v>
       </c>
       <c r="C115">
-        <v>5500</v>
+        <v>12900</v>
       </c>
       <c r="D115">
-        <v>5500</v>
+        <v>12900</v>
       </c>
       <c r="E115">
         <v>0</v>
       </c>
       <c r="F115" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G115" t="str">
         <v>Second</v>
@@ -3750,28 +3750,28 @@
         <v>UMaT/PG/0115/24</v>
       </c>
       <c r="B116" t="str">
-        <v>Abena Akuffo</v>
+        <v>Serwa Appiah</v>
       </c>
       <c r="C116">
-        <v>8800</v>
+        <v>7600</v>
       </c>
       <c r="D116">
-        <v>4500</v>
+        <v>7600</v>
       </c>
       <c r="E116">
-        <v>4300</v>
+        <v>0</v>
       </c>
       <c r="F116" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G116" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H116" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I116" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="117">
@@ -3779,22 +3779,22 @@
         <v>UMaT/PG/0116/24</v>
       </c>
       <c r="B117" t="str">
-        <v>Araba Ofori</v>
+        <v>Kwabena Addo</v>
       </c>
       <c r="C117">
-        <v>10700</v>
+        <v>10400</v>
       </c>
       <c r="D117">
         <v>0</v>
       </c>
       <c r="E117">
-        <v>10700</v>
+        <v>10400</v>
       </c>
       <c r="F117" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G117" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H117" t="str">
         <v>N/A</v>
@@ -3808,19 +3808,19 @@
         <v>UMaT/PG/0117/24</v>
       </c>
       <c r="B118" t="str">
-        <v>Yaa Quaye</v>
+        <v>Esi Danquah</v>
       </c>
       <c r="C118">
-        <v>8400</v>
+        <v>9000</v>
       </c>
       <c r="D118">
-        <v>8400</v>
+        <v>5700</v>
       </c>
       <c r="E118">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="F118" t="str">
-        <v>2025/2026</v>
+        <v>2024/2025</v>
       </c>
       <c r="G118" t="str">
         <v>Second</v>
@@ -3829,7 +3829,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I118" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="119">
@@ -3837,19 +3837,19 @@
         <v>UMaT/PG/0118/24</v>
       </c>
       <c r="B119" t="str">
-        <v>Kobina Akuffo</v>
+        <v>Kwesi Yeboah</v>
       </c>
       <c r="C119">
-        <v>5200</v>
+        <v>10400</v>
       </c>
       <c r="D119">
-        <v>5900</v>
+        <v>10900</v>
       </c>
       <c r="E119">
-        <v>-700</v>
+        <v>-500</v>
       </c>
       <c r="F119" t="str">
-        <v>2025/2026</v>
+        <v>2024/2025</v>
       </c>
       <c r="G119" t="str">
         <v>Second</v>
@@ -3866,19 +3866,19 @@
         <v>UMaT/PG/0119/24</v>
       </c>
       <c r="B120" t="str">
-        <v>Kwesi Akuffo</v>
+        <v>Kodwo Afriyie</v>
       </c>
       <c r="C120">
-        <v>12200</v>
+        <v>7700</v>
       </c>
       <c r="D120">
-        <v>4200</v>
+        <v>5100</v>
       </c>
       <c r="E120">
-        <v>8000</v>
+        <v>2600</v>
       </c>
       <c r="F120" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G120" t="str">
         <v>First</v>
@@ -3895,13 +3895,13 @@
         <v>UMaT/PG/0120/24</v>
       </c>
       <c r="B121" t="str">
-        <v>Araba Agyemang</v>
+        <v>Kakra Mensah</v>
       </c>
       <c r="C121">
-        <v>11700</v>
+        <v>11000</v>
       </c>
       <c r="D121">
-        <v>11700</v>
+        <v>11000</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -3910,7 +3910,7 @@
         <v>2025/2026</v>
       </c>
       <c r="G121" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H121" t="str">
         <v>Bank Transfer</v>
@@ -3924,28 +3924,28 @@
         <v>UMaT/PG/0121/24</v>
       </c>
       <c r="B122" t="str">
-        <v>Ekua Boakye</v>
+        <v>Yaw Ansah</v>
       </c>
       <c r="C122">
-        <v>9000</v>
+        <v>9700</v>
       </c>
       <c r="D122">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="E122">
-        <v>0</v>
+        <v>9700</v>
       </c>
       <c r="F122" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G122" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H122" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I122" t="str">
-        <v>Paid</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="123">
@@ -3953,16 +3953,16 @@
         <v>UMaT/PG/0122/24</v>
       </c>
       <c r="B123" t="str">
-        <v>Panyin Danquah</v>
+        <v>Kwame Sarpong</v>
       </c>
       <c r="C123">
-        <v>5200</v>
+        <v>9700</v>
       </c>
       <c r="D123">
-        <v>5200</v>
+        <v>6900</v>
       </c>
       <c r="E123">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="F123" t="str">
         <v>2024/2025</v>
@@ -3974,7 +3974,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I123" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="124">
@@ -3982,22 +3982,22 @@
         <v>UMaT/PG/0123/24</v>
       </c>
       <c r="B124" t="str">
-        <v>Ama Amoah</v>
+        <v>Afia Asante</v>
       </c>
       <c r="C124">
-        <v>10300</v>
+        <v>9500</v>
       </c>
       <c r="D124">
-        <v>7400</v>
+        <v>5700</v>
       </c>
       <c r="E124">
-        <v>2900</v>
+        <v>3800</v>
       </c>
       <c r="F124" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G124" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H124" t="str">
         <v>Bank Transfer</v>
@@ -4011,28 +4011,28 @@
         <v>UMaT/PG/0124/24</v>
       </c>
       <c r="B125" t="str">
-        <v>Efua Boakye</v>
+        <v>Ekua Gyasi</v>
       </c>
       <c r="C125">
-        <v>12200</v>
+        <v>6200</v>
       </c>
       <c r="D125">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="E125">
-        <v>12200</v>
+        <v>1100</v>
       </c>
       <c r="F125" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G125" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H125" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I125" t="str">
-        <v>Unpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="126">
@@ -4040,19 +4040,19 @@
         <v>UMaT/PG/0125/24</v>
       </c>
       <c r="B126" t="str">
-        <v>Araba Ansah</v>
+        <v>Esi Annan</v>
       </c>
       <c r="C126">
-        <v>11800</v>
+        <v>7900</v>
       </c>
       <c r="D126">
-        <v>8200</v>
+        <v>7900</v>
       </c>
       <c r="E126">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="F126" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G126" t="str">
         <v>First</v>
@@ -4061,7 +4061,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I126" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="127">
@@ -4069,28 +4069,28 @@
         <v>UMaT/PG/0126/24</v>
       </c>
       <c r="B127" t="str">
-        <v>Kodwo Wiredu</v>
+        <v>Abena Wiredu</v>
       </c>
       <c r="C127">
-        <v>9500</v>
+        <v>8600</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>8600</v>
       </c>
       <c r="E127">
-        <v>9500</v>
+        <v>0</v>
       </c>
       <c r="F127" t="str">
         <v>2025/2026</v>
       </c>
       <c r="G127" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H127" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I127" t="str">
-        <v>Unpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="128">
@@ -4098,13 +4098,13 @@
         <v>UMaT/PG/0127/24</v>
       </c>
       <c r="B128" t="str">
-        <v>Mensah Addo</v>
+        <v>Akua Frimpong</v>
       </c>
       <c r="C128">
-        <v>10100</v>
+        <v>5700</v>
       </c>
       <c r="D128">
-        <v>10600</v>
+        <v>6200</v>
       </c>
       <c r="E128">
         <v>-500</v>
@@ -4127,28 +4127,28 @@
         <v>UMaT/PG/0128/24</v>
       </c>
       <c r="B129" t="str">
-        <v>Serwa Agyei</v>
+        <v>Kwesi Yeboah</v>
       </c>
       <c r="C129">
-        <v>10200</v>
+        <v>5300</v>
       </c>
       <c r="D129">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="E129">
-        <v>5700</v>
+        <v>5300</v>
       </c>
       <c r="F129" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G129" t="str">
         <v>First</v>
       </c>
       <c r="H129" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I129" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="130">
@@ -4156,28 +4156,28 @@
         <v>UMaT/PG/0129/24</v>
       </c>
       <c r="B130" t="str">
-        <v>Akua Owusu</v>
+        <v>Kwaku Agyemang</v>
       </c>
       <c r="C130">
-        <v>7700</v>
+        <v>8100</v>
       </c>
       <c r="D130">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="E130">
-        <v>1700</v>
+        <v>8100</v>
       </c>
       <c r="F130" t="str">
         <v>2024/2025</v>
       </c>
       <c r="G130" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H130" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I130" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="131">
@@ -4185,16 +4185,16 @@
         <v>UMaT/PG/0130/24</v>
       </c>
       <c r="B131" t="str">
-        <v>Ato Nkrumah</v>
+        <v>Panyin Frimpong</v>
       </c>
       <c r="C131">
-        <v>7200</v>
+        <v>11500</v>
       </c>
       <c r="D131">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="E131">
-        <v>3600</v>
+        <v>11500</v>
       </c>
       <c r="F131" t="str">
         <v>2024/2025</v>
@@ -4203,10 +4203,10 @@
         <v>Second</v>
       </c>
       <c r="H131" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I131" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="132">
@@ -4214,22 +4214,22 @@
         <v>UMaT/PG/0131/24</v>
       </c>
       <c r="B132" t="str">
-        <v>Kwesi Nkrumah</v>
+        <v>Afi Boateng</v>
       </c>
       <c r="C132">
-        <v>10100</v>
+        <v>5600</v>
       </c>
       <c r="D132">
+        <v>1400</v>
+      </c>
+      <c r="E132">
         <v>4200</v>
       </c>
-      <c r="E132">
-        <v>5900</v>
-      </c>
       <c r="F132" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G132" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H132" t="str">
         <v>Bank Transfer</v>
@@ -4243,19 +4243,19 @@
         <v>UMaT/PG/0132/24</v>
       </c>
       <c r="B133" t="str">
-        <v>Adjoa Afriyie</v>
+        <v>Kwesi Boakye</v>
       </c>
       <c r="C133">
-        <v>10900</v>
+        <v>7600</v>
       </c>
       <c r="D133">
-        <v>10900</v>
+        <v>7600</v>
       </c>
       <c r="E133">
         <v>0</v>
       </c>
       <c r="F133" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G133" t="str">
         <v>First</v>
@@ -4272,28 +4272,28 @@
         <v>UMaT/PG/0133/24</v>
       </c>
       <c r="B134" t="str">
-        <v>Serwa Agyei</v>
+        <v>Afia Akuffo</v>
       </c>
       <c r="C134">
-        <v>10300</v>
+        <v>10900</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="E134">
-        <v>10300</v>
+        <v>7900</v>
       </c>
       <c r="F134" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G134" t="str">
         <v>Second</v>
       </c>
       <c r="H134" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I134" t="str">
-        <v>Unpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="135">
@@ -4301,16 +4301,16 @@
         <v>UMaT/PG/0134/24</v>
       </c>
       <c r="B135" t="str">
-        <v>Panyin Ofori</v>
+        <v>Kwabena Ansah</v>
       </c>
       <c r="C135">
-        <v>7900</v>
+        <v>9600</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="E135">
-        <v>7900</v>
+        <v>2100</v>
       </c>
       <c r="F135" t="str">
         <v>2025/2026</v>
@@ -4319,10 +4319,10 @@
         <v>Second</v>
       </c>
       <c r="H135" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I135" t="str">
-        <v>Unpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="136">
@@ -4330,19 +4330,19 @@
         <v>UMaT/PG/0135/24</v>
       </c>
       <c r="B136" t="str">
-        <v>Akosua Amoah</v>
+        <v>Ebo Amankwah</v>
       </c>
       <c r="C136">
-        <v>9200</v>
+        <v>10500</v>
       </c>
       <c r="D136">
-        <v>3900</v>
+        <v>6300</v>
       </c>
       <c r="E136">
-        <v>5300</v>
+        <v>4200</v>
       </c>
       <c r="F136" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G136" t="str">
         <v>Second</v>
@@ -4359,28 +4359,28 @@
         <v>UMaT/PG/0136/24</v>
       </c>
       <c r="B137" t="str">
-        <v>Serwa Yeboah</v>
+        <v>Mansa Boateng</v>
       </c>
       <c r="C137">
-        <v>9100</v>
+        <v>9900</v>
       </c>
       <c r="D137">
-        <v>9100</v>
+        <v>3100</v>
       </c>
       <c r="E137">
-        <v>0</v>
+        <v>6800</v>
       </c>
       <c r="F137" t="str">
-        <v>2025/2026</v>
+        <v>2024/2025</v>
       </c>
       <c r="G137" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H137" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I137" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="138">
@@ -4388,28 +4388,28 @@
         <v>UMaT/PG/0137/24</v>
       </c>
       <c r="B138" t="str">
-        <v>Araba Owusu</v>
+        <v>Esi Mensah</v>
       </c>
       <c r="C138">
-        <v>13000</v>
+        <v>10900</v>
       </c>
       <c r="D138">
-        <v>13000</v>
+        <v>5400</v>
       </c>
       <c r="E138">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="F138" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G138" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H138" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I138" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="139">
@@ -4417,28 +4417,28 @@
         <v>UMaT/PG/0138/24</v>
       </c>
       <c r="B139" t="str">
-        <v>Kojo Amankwah</v>
+        <v>Ama Boateng</v>
       </c>
       <c r="C139">
-        <v>8500</v>
+        <v>9200</v>
       </c>
       <c r="D139">
-        <v>7700</v>
+        <v>0</v>
       </c>
       <c r="E139">
-        <v>800</v>
+        <v>9200</v>
       </c>
       <c r="F139" t="str">
         <v>2024/2025</v>
       </c>
       <c r="G139" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H139" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I139" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="140">
@@ -4446,19 +4446,19 @@
         <v>UMaT/PG/0139/24</v>
       </c>
       <c r="B140" t="str">
-        <v>Ebo Mensah</v>
+        <v>Akua Quaye</v>
       </c>
       <c r="C140">
-        <v>6400</v>
+        <v>10800</v>
       </c>
       <c r="D140">
-        <v>6400</v>
+        <v>9700</v>
       </c>
       <c r="E140">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="F140" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G140" t="str">
         <v>First</v>
@@ -4467,7 +4467,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I140" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="141">
@@ -4475,28 +4475,28 @@
         <v>UMaT/PG/0140/24</v>
       </c>
       <c r="B141" t="str">
-        <v>Kwabena Danquah</v>
+        <v>Kakra Wiredu</v>
       </c>
       <c r="C141">
-        <v>8700</v>
+        <v>11100</v>
       </c>
       <c r="D141">
-        <v>4800</v>
+        <v>0</v>
       </c>
       <c r="E141">
-        <v>3900</v>
+        <v>11100</v>
       </c>
       <c r="F141" t="str">
-        <v>2025/2026</v>
+        <v>2024/2025</v>
       </c>
       <c r="G141" t="str">
         <v>Second</v>
       </c>
       <c r="H141" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I141" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="142">
@@ -4504,28 +4504,28 @@
         <v>UMaT/PG/0141/24</v>
       </c>
       <c r="B142" t="str">
-        <v>Esi Sarpong</v>
+        <v>Esi Boateng</v>
       </c>
       <c r="C142">
-        <v>8800</v>
+        <v>10400</v>
       </c>
       <c r="D142">
-        <v>7500</v>
+        <v>10400</v>
       </c>
       <c r="E142">
-        <v>1300</v>
+        <v>0</v>
       </c>
       <c r="F142" t="str">
-        <v>2025/2026</v>
+        <v>2024/2025</v>
       </c>
       <c r="G142" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H142" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I142" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="143">
@@ -4533,19 +4533,19 @@
         <v>UMaT/PG/0142/24</v>
       </c>
       <c r="B143" t="str">
-        <v>Abena Sarpong</v>
+        <v>Ama Gyasi</v>
       </c>
       <c r="C143">
-        <v>11500</v>
+        <v>12100</v>
       </c>
       <c r="D143">
-        <v>6800</v>
+        <v>3500</v>
       </c>
       <c r="E143">
-        <v>4700</v>
+        <v>8600</v>
       </c>
       <c r="F143" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G143" t="str">
         <v>Second</v>
@@ -4562,19 +4562,19 @@
         <v>UMaT/PG/0143/24</v>
       </c>
       <c r="B144" t="str">
-        <v>Serwa Osei</v>
+        <v>Kwame Boateng</v>
       </c>
       <c r="C144">
-        <v>10100</v>
+        <v>9100</v>
       </c>
       <c r="D144">
-        <v>8300</v>
+        <v>7700</v>
       </c>
       <c r="E144">
-        <v>1800</v>
+        <v>1400</v>
       </c>
       <c r="F144" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G144" t="str">
         <v>First</v>
@@ -4591,28 +4591,28 @@
         <v>UMaT/PG/0144/24</v>
       </c>
       <c r="B145" t="str">
-        <v>Kojo Owusu</v>
+        <v>Efua Owusu</v>
       </c>
       <c r="C145">
-        <v>6400</v>
+        <v>10500</v>
       </c>
       <c r="D145">
-        <v>6400</v>
+        <v>0</v>
       </c>
       <c r="E145">
-        <v>0</v>
+        <v>10500</v>
       </c>
       <c r="F145" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G145" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H145" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I145" t="str">
-        <v>Paid</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="146">
@@ -4620,22 +4620,22 @@
         <v>UMaT/PG/0145/24</v>
       </c>
       <c r="B146" t="str">
-        <v>Ama Boakye</v>
+        <v>Akua Annan</v>
       </c>
       <c r="C146">
-        <v>12000</v>
+        <v>9500</v>
       </c>
       <c r="D146">
         <v>0</v>
       </c>
       <c r="E146">
-        <v>12000</v>
+        <v>9500</v>
       </c>
       <c r="F146" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G146" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H146" t="str">
         <v>N/A</v>
@@ -4649,16 +4649,16 @@
         <v>UMaT/PG/0146/24</v>
       </c>
       <c r="B147" t="str">
-        <v>Kwame Darko</v>
+        <v>Mensah Agyemang</v>
       </c>
       <c r="C147">
-        <v>7600</v>
+        <v>5900</v>
       </c>
       <c r="D147">
-        <v>8900</v>
+        <v>0</v>
       </c>
       <c r="E147">
-        <v>-1300</v>
+        <v>5900</v>
       </c>
       <c r="F147" t="str">
         <v>2024/2025</v>
@@ -4667,10 +4667,10 @@
         <v>Second</v>
       </c>
       <c r="H147" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I147" t="str">
-        <v>Overpaid</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="148">
@@ -4678,28 +4678,28 @@
         <v>UMaT/PG/0147/24</v>
       </c>
       <c r="B148" t="str">
-        <v>Efua Osei</v>
+        <v>Ama Amoah</v>
       </c>
       <c r="C148">
-        <v>12500</v>
+        <v>9100</v>
       </c>
       <c r="D148">
-        <v>6900</v>
+        <v>9100</v>
       </c>
       <c r="E148">
-        <v>5600</v>
+        <v>0</v>
       </c>
       <c r="F148" t="str">
         <v>2024/2025</v>
       </c>
       <c r="G148" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H148" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I148" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="149">
@@ -4707,16 +4707,16 @@
         <v>UMaT/PG/0148/24</v>
       </c>
       <c r="B149" t="str">
-        <v>Kwaku Annan</v>
+        <v>Serwa Wiredu</v>
       </c>
       <c r="C149">
-        <v>7300</v>
+        <v>6400</v>
       </c>
       <c r="D149">
-        <v>7300</v>
+        <v>3400</v>
       </c>
       <c r="E149">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F149" t="str">
         <v>2024/2025</v>
@@ -4728,7 +4728,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I149" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="150">
@@ -4736,22 +4736,22 @@
         <v>UMaT/PG/0149/24</v>
       </c>
       <c r="B150" t="str">
-        <v>Ebo Boateng</v>
+        <v>Ebo Quaye</v>
       </c>
       <c r="C150">
-        <v>6300</v>
+        <v>6400</v>
       </c>
       <c r="D150">
-        <v>5500</v>
+        <v>2700</v>
       </c>
       <c r="E150">
-        <v>800</v>
+        <v>3700</v>
       </c>
       <c r="F150" t="str">
         <v>2023/2024</v>
       </c>
       <c r="G150" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H150" t="str">
         <v>Bank Transfer</v>
@@ -4765,16 +4765,16 @@
         <v>UMaT/PG/0150/24</v>
       </c>
       <c r="B151" t="str">
-        <v>Akosua Boakye</v>
+        <v>Kodwo Mensah</v>
       </c>
       <c r="C151">
-        <v>12500</v>
+        <v>11900</v>
       </c>
       <c r="D151">
-        <v>12500</v>
+        <v>0</v>
       </c>
       <c r="E151">
-        <v>0</v>
+        <v>11900</v>
       </c>
       <c r="F151" t="str">
         <v>2024/2025</v>
@@ -4783,10 +4783,10 @@
         <v>First</v>
       </c>
       <c r="H151" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I151" t="str">
-        <v>Paid</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="152">
@@ -4794,19 +4794,19 @@
         <v>UMaT/PG/0151/24</v>
       </c>
       <c r="B152" t="str">
-        <v>Kwesi Ofori</v>
+        <v>Kojo Opoku</v>
       </c>
       <c r="C152">
-        <v>7400</v>
+        <v>6400</v>
       </c>
       <c r="D152">
-        <v>7400</v>
+        <v>6400</v>
       </c>
       <c r="E152">
         <v>0</v>
       </c>
       <c r="F152" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G152" t="str">
         <v>Second</v>
@@ -4823,28 +4823,28 @@
         <v>UMaT/PG/0152/24</v>
       </c>
       <c r="B153" t="str">
-        <v>Efua Akuffo</v>
+        <v>Kobina Appiah</v>
       </c>
       <c r="C153">
-        <v>5400</v>
+        <v>5800</v>
       </c>
       <c r="D153">
-        <v>5400</v>
+        <v>3100</v>
       </c>
       <c r="E153">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="F153" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G153" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H153" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I153" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="154">
@@ -4852,13 +4852,13 @@
         <v>UMaT/PG/0153/24</v>
       </c>
       <c r="B154" t="str">
-        <v>Serwa Amoah</v>
+        <v>Efua Frimpong</v>
       </c>
       <c r="C154">
-        <v>10300</v>
+        <v>9200</v>
       </c>
       <c r="D154">
-        <v>10300</v>
+        <v>9200</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -4881,22 +4881,22 @@
         <v>UMaT/PG/0154/24</v>
       </c>
       <c r="B155" t="str">
-        <v>Kwadwo Asante</v>
+        <v>Kwabena Nkrumah</v>
       </c>
       <c r="C155">
-        <v>9400</v>
+        <v>10100</v>
       </c>
       <c r="D155">
-        <v>8700</v>
+        <v>6700</v>
       </c>
       <c r="E155">
-        <v>700</v>
+        <v>3400</v>
       </c>
       <c r="F155" t="str">
-        <v>2025/2026</v>
+        <v>2024/2025</v>
       </c>
       <c r="G155" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H155" t="str">
         <v>Bank Transfer</v>
@@ -4910,28 +4910,28 @@
         <v>UMaT/PG/0155/24</v>
       </c>
       <c r="B156" t="str">
-        <v>Afia Afriyie</v>
+        <v>Akua Gyasi</v>
       </c>
       <c r="C156">
-        <v>12900</v>
+        <v>9300</v>
       </c>
       <c r="D156">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="E156">
-        <v>12900</v>
+        <v>-1700</v>
       </c>
       <c r="F156" t="str">
-        <v>2025/2026</v>
+        <v>2024/2025</v>
       </c>
       <c r="G156" t="str">
         <v>First</v>
       </c>
       <c r="H156" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I156" t="str">
-        <v>Unpaid</v>
+        <v>Overpaid</v>
       </c>
     </row>
     <row r="157">
@@ -4939,28 +4939,28 @@
         <v>UMaT/PG/0156/24</v>
       </c>
       <c r="B157" t="str">
-        <v>Kojo Mensah</v>
+        <v>Afi Amoah</v>
       </c>
       <c r="C157">
-        <v>5400</v>
+        <v>9900</v>
       </c>
       <c r="D157">
-        <v>0</v>
+        <v>9900</v>
       </c>
       <c r="E157">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="F157" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G157" t="str">
         <v>Second</v>
       </c>
       <c r="H157" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I157" t="str">
-        <v>Unpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="158">
@@ -4968,28 +4968,28 @@
         <v>UMaT/PG/0157/24</v>
       </c>
       <c r="B158" t="str">
-        <v>Ama Owusu</v>
+        <v>Serwa Yeboah</v>
       </c>
       <c r="C158">
-        <v>5100</v>
+        <v>7500</v>
       </c>
       <c r="D158">
-        <v>3800</v>
+        <v>0</v>
       </c>
       <c r="E158">
-        <v>1300</v>
+        <v>7500</v>
       </c>
       <c r="F158" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G158" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H158" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I158" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="159">
@@ -4997,13 +4997,13 @@
         <v>UMaT/PG/0158/24</v>
       </c>
       <c r="B159" t="str">
-        <v>Kwabena Sarpong</v>
+        <v>Kofi Owusu</v>
       </c>
       <c r="C159">
-        <v>9900</v>
+        <v>8200</v>
       </c>
       <c r="D159">
-        <v>9900</v>
+        <v>8200</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>2025/2026</v>
       </c>
       <c r="G159" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H159" t="str">
         <v>Bank Transfer</v>
@@ -5026,16 +5026,16 @@
         <v>UMaT/PG/0159/24</v>
       </c>
       <c r="B160" t="str">
-        <v>Mensah Addo</v>
+        <v>Kobina Afriyie</v>
       </c>
       <c r="C160">
         <v>10800</v>
       </c>
       <c r="D160">
-        <v>7000</v>
+        <v>7200</v>
       </c>
       <c r="E160">
-        <v>3800</v>
+        <v>3600</v>
       </c>
       <c r="F160" t="str">
         <v>2025/2026</v>
@@ -5055,28 +5055,28 @@
         <v>UMaT/PG/0160/24</v>
       </c>
       <c r="B161" t="str">
-        <v>Araba Appiah</v>
+        <v>Kakra Danquah</v>
       </c>
       <c r="C161">
-        <v>6900</v>
+        <v>10800</v>
       </c>
       <c r="D161">
-        <v>3000</v>
+        <v>10800</v>
       </c>
       <c r="E161">
-        <v>3900</v>
+        <v>0</v>
       </c>
       <c r="F161" t="str">
-        <v>2025/2026</v>
+        <v>2024/2025</v>
       </c>
       <c r="G161" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H161" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I161" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="162">
@@ -5084,19 +5084,19 @@
         <v>UMaT/PG/0161/24</v>
       </c>
       <c r="B162" t="str">
-        <v>Kwesi Sarpong</v>
+        <v>Kwame Boakye</v>
       </c>
       <c r="C162">
-        <v>8700</v>
+        <v>5000</v>
       </c>
       <c r="D162">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="E162">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="F162" t="str">
-        <v>2025/2026</v>
+        <v>2024/2025</v>
       </c>
       <c r="G162" t="str">
         <v>Second</v>
@@ -5105,7 +5105,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I162" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="163">
@@ -5113,19 +5113,19 @@
         <v>UMaT/PG/0162/24</v>
       </c>
       <c r="B163" t="str">
-        <v>Adwoa Mensah</v>
+        <v>Panyin Darko</v>
       </c>
       <c r="C163">
-        <v>6400</v>
+        <v>9400</v>
       </c>
       <c r="D163">
-        <v>3200</v>
+        <v>6700</v>
       </c>
       <c r="E163">
-        <v>3200</v>
+        <v>2700</v>
       </c>
       <c r="F163" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G163" t="str">
         <v>First</v>
@@ -5142,28 +5142,28 @@
         <v>UMaT/PG/0163/24</v>
       </c>
       <c r="B164" t="str">
-        <v>Akua Yeboah</v>
+        <v>Ekua Agyei</v>
       </c>
       <c r="C164">
-        <v>11700</v>
+        <v>11500</v>
       </c>
       <c r="D164">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="E164">
-        <v>11700</v>
+        <v>8000</v>
       </c>
       <c r="F164" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G164" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H164" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I164" t="str">
-        <v>Unpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="165">
@@ -5171,28 +5171,28 @@
         <v>UMaT/PG/0164/24</v>
       </c>
       <c r="B165" t="str">
-        <v>Kakra Amoah</v>
+        <v>Yaa Frimpong</v>
       </c>
       <c r="C165">
-        <v>6900</v>
+        <v>12700</v>
       </c>
       <c r="D165">
-        <v>2800</v>
+        <v>12700</v>
       </c>
       <c r="E165">
-        <v>4100</v>
+        <v>0</v>
       </c>
       <c r="F165" t="str">
         <v>2025/2026</v>
       </c>
       <c r="G165" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H165" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I165" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="166">
@@ -5200,28 +5200,28 @@
         <v>UMaT/PG/0165/24</v>
       </c>
       <c r="B166" t="str">
-        <v>Kofi Appiah</v>
+        <v>Ekua Owusu</v>
       </c>
       <c r="C166">
-        <v>8700</v>
+        <v>11300</v>
       </c>
       <c r="D166">
-        <v>9300</v>
+        <v>11300</v>
       </c>
       <c r="E166">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="F166" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G166" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H166" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I166" t="str">
-        <v>Overpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="167">
@@ -5229,28 +5229,28 @@
         <v>UMaT/PG/0166/24</v>
       </c>
       <c r="B167" t="str">
-        <v>Mansa Asante</v>
+        <v>Yaa Opoku</v>
       </c>
       <c r="C167">
-        <v>6200</v>
+        <v>9800</v>
       </c>
       <c r="D167">
-        <v>6200</v>
+        <v>8900</v>
       </c>
       <c r="E167">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F167" t="str">
         <v>2023/2024</v>
       </c>
       <c r="G167" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H167" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I167" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="168">
@@ -5258,19 +5258,19 @@
         <v>UMaT/PG/0167/24</v>
       </c>
       <c r="B168" t="str">
-        <v>Ama Mensah</v>
+        <v>Mensah Annan</v>
       </c>
       <c r="C168">
-        <v>12500</v>
+        <v>10800</v>
       </c>
       <c r="D168">
-        <v>12500</v>
+        <v>10800</v>
       </c>
       <c r="E168">
         <v>0</v>
       </c>
       <c r="F168" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G168" t="str">
         <v>Second</v>
@@ -5287,28 +5287,28 @@
         <v>UMaT/PG/0168/24</v>
       </c>
       <c r="B169" t="str">
-        <v>Ato Wiredu</v>
+        <v>Kojo Agyemang</v>
       </c>
       <c r="C169">
-        <v>9800</v>
+        <v>7800</v>
       </c>
       <c r="D169">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="E169">
-        <v>9800</v>
+        <v>2400</v>
       </c>
       <c r="F169" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G169" t="str">
         <v>First</v>
       </c>
       <c r="H169" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I169" t="str">
-        <v>Unpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="170">
@@ -5316,19 +5316,19 @@
         <v>UMaT/PG/0169/24</v>
       </c>
       <c r="B170" t="str">
-        <v>Mansa Quaye</v>
+        <v>Abena Quaye</v>
       </c>
       <c r="C170">
-        <v>7200</v>
+        <v>9600</v>
       </c>
       <c r="D170">
-        <v>7200</v>
+        <v>4300</v>
       </c>
       <c r="E170">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="F170" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G170" t="str">
         <v>First</v>
@@ -5337,7 +5337,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I170" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="171">
@@ -5345,19 +5345,19 @@
         <v>UMaT/PG/0170/24</v>
       </c>
       <c r="B171" t="str">
-        <v>Kwesi Amankwah</v>
+        <v>Kojo Osei</v>
       </c>
       <c r="C171">
-        <v>8000</v>
+        <v>10800</v>
       </c>
       <c r="D171">
-        <v>8000</v>
+        <v>10800</v>
       </c>
       <c r="E171">
         <v>0</v>
       </c>
       <c r="F171" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G171" t="str">
         <v>First</v>
@@ -5374,16 +5374,16 @@
         <v>UMaT/PG/0171/24</v>
       </c>
       <c r="B172" t="str">
-        <v>Serwa Osei</v>
+        <v>Kwadwo Akuffo</v>
       </c>
       <c r="C172">
-        <v>6500</v>
+        <v>8700</v>
       </c>
       <c r="D172">
-        <v>6500</v>
+        <v>10100</v>
       </c>
       <c r="E172">
-        <v>0</v>
+        <v>-1400</v>
       </c>
       <c r="F172" t="str">
         <v>2023/2024</v>
@@ -5395,7 +5395,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I172" t="str">
-        <v>Paid</v>
+        <v>Overpaid</v>
       </c>
     </row>
     <row r="173">
@@ -5403,19 +5403,19 @@
         <v>UMaT/PG/0172/24</v>
       </c>
       <c r="B173" t="str">
-        <v>Kwabena Gyasi</v>
+        <v>Esi Ansah</v>
       </c>
       <c r="C173">
-        <v>8500</v>
+        <v>6900</v>
       </c>
       <c r="D173">
-        <v>8500</v>
+        <v>6900</v>
       </c>
       <c r="E173">
         <v>0</v>
       </c>
       <c r="F173" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G173" t="str">
         <v>First</v>
@@ -5432,13 +5432,13 @@
         <v>UMaT/PG/0173/24</v>
       </c>
       <c r="B174" t="str">
-        <v>Panyin Agyei</v>
+        <v>Ato Osei</v>
       </c>
       <c r="C174">
-        <v>6800</v>
+        <v>12600</v>
       </c>
       <c r="D174">
-        <v>6800</v>
+        <v>12600</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -5447,7 +5447,7 @@
         <v>2024/2025</v>
       </c>
       <c r="G174" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H174" t="str">
         <v>Bank Transfer</v>
@@ -5461,28 +5461,28 @@
         <v>UMaT/PG/0174/24</v>
       </c>
       <c r="B175" t="str">
-        <v>Abena Amoah</v>
+        <v>Akua Asante</v>
       </c>
       <c r="C175">
-        <v>6800</v>
+        <v>5900</v>
       </c>
       <c r="D175">
-        <v>6800</v>
+        <v>0</v>
       </c>
       <c r="E175">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="F175" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G175" t="str">
         <v>Second</v>
       </c>
       <c r="H175" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I175" t="str">
-        <v>Paid</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="176">
@@ -5490,28 +5490,28 @@
         <v>UMaT/PG/0175/24</v>
       </c>
       <c r="B176" t="str">
-        <v>Ato Wiredu</v>
+        <v>Adwoa Acheampong</v>
       </c>
       <c r="C176">
-        <v>6100</v>
+        <v>9400</v>
       </c>
       <c r="D176">
-        <v>0</v>
+        <v>9400</v>
       </c>
       <c r="E176">
-        <v>6100</v>
+        <v>0</v>
       </c>
       <c r="F176" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G176" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H176" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I176" t="str">
-        <v>Unpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="177">
@@ -5519,28 +5519,28 @@
         <v>UMaT/PG/0176/24</v>
       </c>
       <c r="B177" t="str">
-        <v>Kwabena Owusu</v>
+        <v>Kwesi Opoku</v>
       </c>
       <c r="C177">
-        <v>13000</v>
+        <v>8900</v>
       </c>
       <c r="D177">
-        <v>4700</v>
+        <v>8900</v>
       </c>
       <c r="E177">
-        <v>8300</v>
+        <v>0</v>
       </c>
       <c r="F177" t="str">
         <v>2024/2025</v>
       </c>
       <c r="G177" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H177" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I177" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="178">
@@ -5548,19 +5548,19 @@
         <v>UMaT/PG/0177/24</v>
       </c>
       <c r="B178" t="str">
-        <v>Mensah Agyei</v>
+        <v>Mensah Mensah</v>
       </c>
       <c r="C178">
-        <v>6700</v>
+        <v>11200</v>
       </c>
       <c r="D178">
-        <v>5700</v>
+        <v>11200</v>
       </c>
       <c r="E178">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F178" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G178" t="str">
         <v>Second</v>
@@ -5569,7 +5569,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I178" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="179">
@@ -5577,28 +5577,28 @@
         <v>UMaT/PG/0178/24</v>
       </c>
       <c r="B179" t="str">
-        <v>Kodwo Ansah</v>
+        <v>Afia Agyemang</v>
       </c>
       <c r="C179">
-        <v>7600</v>
+        <v>9800</v>
       </c>
       <c r="D179">
-        <v>6800</v>
+        <v>9800</v>
       </c>
       <c r="E179">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="F179" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G179" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H179" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I179" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="180">
@@ -5606,28 +5606,28 @@
         <v>UMaT/PG/0179/24</v>
       </c>
       <c r="B180" t="str">
-        <v>Abena Mensah</v>
+        <v>Serwa Amoah</v>
       </c>
       <c r="C180">
-        <v>5200</v>
+        <v>8700</v>
       </c>
       <c r="D180">
-        <v>5200</v>
+        <v>10100</v>
       </c>
       <c r="E180">
-        <v>0</v>
+        <v>-1400</v>
       </c>
       <c r="F180" t="str">
         <v>2025/2026</v>
       </c>
       <c r="G180" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H180" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I180" t="str">
-        <v>Paid</v>
+        <v>Overpaid</v>
       </c>
     </row>
     <row r="181">
@@ -5635,28 +5635,28 @@
         <v>UMaT/PG/0180/24</v>
       </c>
       <c r="B181" t="str">
-        <v>Kwabena Boakye</v>
+        <v>Akosua Boateng</v>
       </c>
       <c r="C181">
-        <v>8700</v>
+        <v>9300</v>
       </c>
       <c r="D181">
-        <v>0</v>
+        <v>9300</v>
       </c>
       <c r="E181">
-        <v>8700</v>
+        <v>0</v>
       </c>
       <c r="F181" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G181" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H181" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I181" t="str">
-        <v>Unpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="182">
@@ -5664,28 +5664,28 @@
         <v>UMaT/PG/0181/24</v>
       </c>
       <c r="B182" t="str">
-        <v>Afia Quaye</v>
+        <v>Ebo Acheampong</v>
       </c>
       <c r="C182">
-        <v>7300</v>
+        <v>6200</v>
       </c>
       <c r="D182">
-        <v>2000</v>
+        <v>6200</v>
       </c>
       <c r="E182">
-        <v>5300</v>
+        <v>0</v>
       </c>
       <c r="F182" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G182" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H182" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I182" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="183">
@@ -5693,16 +5693,16 @@
         <v>UMaT/PG/0182/24</v>
       </c>
       <c r="B183" t="str">
-        <v>Yaw Quaye</v>
+        <v>Kobina Wiredu</v>
       </c>
       <c r="C183">
-        <v>10100</v>
+        <v>9200</v>
       </c>
       <c r="D183">
         <v>0</v>
       </c>
       <c r="E183">
-        <v>10100</v>
+        <v>9200</v>
       </c>
       <c r="F183" t="str">
         <v>2024/2025</v>
@@ -5722,16 +5722,16 @@
         <v>UMaT/PG/0183/24</v>
       </c>
       <c r="B184" t="str">
-        <v>Ekua Boakye</v>
+        <v>Akosua Danquah</v>
       </c>
       <c r="C184">
-        <v>12800</v>
+        <v>11200</v>
       </c>
       <c r="D184">
-        <v>7200</v>
+        <v>0</v>
       </c>
       <c r="E184">
-        <v>5600</v>
+        <v>11200</v>
       </c>
       <c r="F184" t="str">
         <v>2023/2024</v>
@@ -5740,10 +5740,10 @@
         <v>First</v>
       </c>
       <c r="H184" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I184" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="185">
@@ -5751,28 +5751,28 @@
         <v>UMaT/PG/0184/24</v>
       </c>
       <c r="B185" t="str">
-        <v>Panyin Afriyie</v>
+        <v>Araba Gyasi</v>
       </c>
       <c r="C185">
-        <v>6400</v>
+        <v>12600</v>
       </c>
       <c r="D185">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="E185">
-        <v>-600</v>
+        <v>12600</v>
       </c>
       <c r="F185" t="str">
         <v>2025/2026</v>
       </c>
       <c r="G185" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H185" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I185" t="str">
-        <v>Overpaid</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="186">
@@ -5780,19 +5780,19 @@
         <v>UMaT/PG/0185/24</v>
       </c>
       <c r="B186" t="str">
-        <v>Adjoa Agyemang</v>
+        <v>Mansa Osei</v>
       </c>
       <c r="C186">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="D186">
-        <v>5300</v>
+        <v>8800</v>
       </c>
       <c r="E186">
-        <v>700</v>
+        <v>3200</v>
       </c>
       <c r="F186" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G186" t="str">
         <v>Second</v>
@@ -5809,19 +5809,19 @@
         <v>UMaT/PG/0186/24</v>
       </c>
       <c r="B187" t="str">
-        <v>Ato Afriyie</v>
+        <v>Kobina Amankwah</v>
       </c>
       <c r="C187">
-        <v>12500</v>
+        <v>12900</v>
       </c>
       <c r="D187">
-        <v>12500</v>
+        <v>8800</v>
       </c>
       <c r="E187">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="F187" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G187" t="str">
         <v>First</v>
@@ -5830,7 +5830,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I187" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="188">
@@ -5838,19 +5838,19 @@
         <v>UMaT/PG/0187/24</v>
       </c>
       <c r="B188" t="str">
-        <v>Afia Boakye</v>
+        <v>Kobina Gyasi</v>
       </c>
       <c r="C188">
         <v>8500</v>
       </c>
       <c r="D188">
-        <v>6200</v>
+        <v>8500</v>
       </c>
       <c r="E188">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="F188" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G188" t="str">
         <v>Second</v>
@@ -5859,7 +5859,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I188" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="189">
@@ -5867,28 +5867,28 @@
         <v>UMaT/PG/0188/24</v>
       </c>
       <c r="B189" t="str">
-        <v>Efua Akuffo</v>
+        <v>Kwadwo Asante</v>
       </c>
       <c r="C189">
-        <v>10500</v>
+        <v>6000</v>
       </c>
       <c r="D189">
-        <v>11500</v>
+        <v>6000</v>
       </c>
       <c r="E189">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="F189" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G189" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H189" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I189" t="str">
-        <v>Overpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="190">
@@ -5896,28 +5896,28 @@
         <v>UMaT/PG/0189/24</v>
       </c>
       <c r="B190" t="str">
-        <v>Mansa Yeboah</v>
+        <v>Efua Darko</v>
       </c>
       <c r="C190">
-        <v>9600</v>
+        <v>12200</v>
       </c>
       <c r="D190">
-        <v>11200</v>
+        <v>12200</v>
       </c>
       <c r="E190">
-        <v>-1600</v>
+        <v>0</v>
       </c>
       <c r="F190" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G190" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H190" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I190" t="str">
-        <v>Overpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="191">
@@ -5925,19 +5925,19 @@
         <v>UMaT/PG/0190/24</v>
       </c>
       <c r="B191" t="str">
-        <v>Akosua Yeboah</v>
+        <v>Adjoa Ofori</v>
       </c>
       <c r="C191">
-        <v>8000</v>
+        <v>12400</v>
       </c>
       <c r="D191">
-        <v>8000</v>
+        <v>11100</v>
       </c>
       <c r="E191">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="F191" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G191" t="str">
         <v>First</v>
@@ -5946,7 +5946,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I191" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="192">
@@ -5954,28 +5954,28 @@
         <v>UMaT/PG/0191/24</v>
       </c>
       <c r="B192" t="str">
-        <v>Afia Ofori</v>
+        <v>Ekua Acheampong</v>
       </c>
       <c r="C192">
-        <v>12200</v>
+        <v>9600</v>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="E192">
-        <v>12200</v>
+        <v>5800</v>
       </c>
       <c r="F192" t="str">
         <v>2025/2026</v>
       </c>
       <c r="G192" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H192" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I192" t="str">
-        <v>Unpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="193">
@@ -5983,19 +5983,19 @@
         <v>UMaT/PG/0192/24</v>
       </c>
       <c r="B193" t="str">
-        <v>Araba Boakye</v>
+        <v>Ekua Mensah</v>
       </c>
       <c r="C193">
-        <v>11600</v>
+        <v>9900</v>
       </c>
       <c r="D193">
-        <v>10100</v>
+        <v>9900</v>
       </c>
       <c r="E193">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="F193" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G193" t="str">
         <v>Second</v>
@@ -6004,7 +6004,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I193" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="194">
@@ -6012,22 +6012,22 @@
         <v>UMaT/PG/0193/24</v>
       </c>
       <c r="B194" t="str">
-        <v>Ekua Yeboah</v>
+        <v>Kwaku Osei</v>
       </c>
       <c r="C194">
-        <v>11900</v>
+        <v>10800</v>
       </c>
       <c r="D194">
         <v>0</v>
       </c>
       <c r="E194">
-        <v>11900</v>
+        <v>10800</v>
       </c>
       <c r="F194" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G194" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H194" t="str">
         <v>N/A</v>
@@ -6041,28 +6041,28 @@
         <v>UMaT/PG/0194/24</v>
       </c>
       <c r="B195" t="str">
-        <v>Ekua Asante</v>
+        <v>Yaw Boakye</v>
       </c>
       <c r="C195">
-        <v>6400</v>
+        <v>8300</v>
       </c>
       <c r="D195">
-        <v>0</v>
+        <v>8300</v>
       </c>
       <c r="E195">
-        <v>6400</v>
+        <v>0</v>
       </c>
       <c r="F195" t="str">
-        <v>2025/2026</v>
+        <v>2024/2025</v>
       </c>
       <c r="G195" t="str">
         <v>First</v>
       </c>
       <c r="H195" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I195" t="str">
-        <v>Unpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="196">
@@ -6070,28 +6070,28 @@
         <v>UMaT/PG/0195/24</v>
       </c>
       <c r="B196" t="str">
-        <v>Ama Acheampong</v>
+        <v>Yaa Gyasi</v>
       </c>
       <c r="C196">
-        <v>6100</v>
+        <v>10600</v>
       </c>
       <c r="D196">
-        <v>6100</v>
+        <v>0</v>
       </c>
       <c r="E196">
-        <v>0</v>
+        <v>10600</v>
       </c>
       <c r="F196" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G196" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H196" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I196" t="str">
-        <v>Paid</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="197">
@@ -6099,19 +6099,19 @@
         <v>UMaT/PG/0196/24</v>
       </c>
       <c r="B197" t="str">
-        <v>Kodwo Gyasi</v>
+        <v>Serwa Ofori</v>
       </c>
       <c r="C197">
-        <v>5600</v>
+        <v>10200</v>
       </c>
       <c r="D197">
-        <v>3500</v>
+        <v>9300</v>
       </c>
       <c r="E197">
-        <v>2100</v>
+        <v>900</v>
       </c>
       <c r="F197" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G197" t="str">
         <v>Second</v>
@@ -6128,16 +6128,16 @@
         <v>UMaT/PG/0197/24</v>
       </c>
       <c r="B198" t="str">
-        <v>Kwabena Ansah</v>
+        <v>Adwoa Appiah</v>
       </c>
       <c r="C198">
-        <v>11100</v>
+        <v>12700</v>
       </c>
       <c r="D198">
-        <v>8100</v>
+        <v>12700</v>
       </c>
       <c r="E198">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="F198" t="str">
         <v>2024/2025</v>
@@ -6149,7 +6149,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I198" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="199">
@@ -6157,28 +6157,28 @@
         <v>UMaT/PG/0198/24</v>
       </c>
       <c r="B199" t="str">
-        <v>Adwoa Amoah</v>
+        <v>Yaw Frimpong</v>
       </c>
       <c r="C199">
-        <v>7600</v>
+        <v>8300</v>
       </c>
       <c r="D199">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="E199">
-        <v>7600</v>
+        <v>5800</v>
       </c>
       <c r="F199" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G199" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H199" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I199" t="str">
-        <v>Unpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="200">
@@ -6186,19 +6186,19 @@
         <v>UMaT/PG/0199/24</v>
       </c>
       <c r="B200" t="str">
-        <v>Kwabena Akuffo</v>
+        <v>Kwame Amoah</v>
       </c>
       <c r="C200">
-        <v>8300</v>
+        <v>7600</v>
       </c>
       <c r="D200">
         <v>0</v>
       </c>
       <c r="E200">
-        <v>8300</v>
+        <v>7600</v>
       </c>
       <c r="F200" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G200" t="str">
         <v>Second</v>
@@ -6215,28 +6215,28 @@
         <v>UMaT/PG/0200/24</v>
       </c>
       <c r="B201" t="str">
-        <v>Kwabena Appiah</v>
+        <v>Abena Asante</v>
       </c>
       <c r="C201">
-        <v>12200</v>
+        <v>11700</v>
       </c>
       <c r="D201">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="E201">
-        <v>12200</v>
+        <v>6500</v>
       </c>
       <c r="F201" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G201" t="str">
         <v>First</v>
       </c>
       <c r="H201" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I201" t="str">
-        <v>Unpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="202">
@@ -6244,28 +6244,28 @@
         <v>UMaT/PG/0201/24</v>
       </c>
       <c r="B202" t="str">
-        <v>Kobina Owusu</v>
+        <v>Mensah Owusu</v>
       </c>
       <c r="C202">
-        <v>9400</v>
+        <v>10200</v>
       </c>
       <c r="D202">
-        <v>4600</v>
+        <v>0</v>
       </c>
       <c r="E202">
-        <v>4800</v>
+        <v>10200</v>
       </c>
       <c r="F202" t="str">
         <v>2025/2026</v>
       </c>
       <c r="G202" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H202" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I202" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="203">
@@ -6273,28 +6273,28 @@
         <v>UMaT/PG/0202/24</v>
       </c>
       <c r="B203" t="str">
-        <v>Kwaku Ofori</v>
+        <v>Kwaku Acheampong</v>
       </c>
       <c r="C203">
-        <v>5100</v>
+        <v>8900</v>
       </c>
       <c r="D203">
-        <v>1300</v>
+        <v>8900</v>
       </c>
       <c r="E203">
-        <v>3800</v>
+        <v>0</v>
       </c>
       <c r="F203" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G203" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H203" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I203" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="204">
@@ -6302,28 +6302,28 @@
         <v>UMaT/PG/0203/24</v>
       </c>
       <c r="B204" t="str">
-        <v>Kwame Sarpong</v>
+        <v>Kakra Ansah</v>
       </c>
       <c r="C204">
-        <v>11000</v>
+        <v>8500</v>
       </c>
       <c r="D204">
-        <v>11000</v>
+        <v>5200</v>
       </c>
       <c r="E204">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="F204" t="str">
-        <v>2025/2026</v>
+        <v>2024/2025</v>
       </c>
       <c r="G204" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H204" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I204" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="205">
@@ -6331,28 +6331,28 @@
         <v>UMaT/PG/0204/24</v>
       </c>
       <c r="B205" t="str">
-        <v>Kodwo Appiah</v>
+        <v>Yaw Boakye</v>
       </c>
       <c r="C205">
-        <v>11600</v>
+        <v>10500</v>
       </c>
       <c r="D205">
-        <v>11600</v>
+        <v>0</v>
       </c>
       <c r="E205">
-        <v>0</v>
+        <v>10500</v>
       </c>
       <c r="F205" t="str">
         <v>2023/2024</v>
       </c>
       <c r="G205" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H205" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I205" t="str">
-        <v>Paid</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="206">
@@ -6360,16 +6360,16 @@
         <v>UMaT/PG/0205/24</v>
       </c>
       <c r="B206" t="str">
-        <v>Akua Agyei</v>
+        <v>Mansa Addo</v>
       </c>
       <c r="C206">
-        <v>12100</v>
+        <v>5100</v>
       </c>
       <c r="D206">
-        <v>12800</v>
+        <v>2900</v>
       </c>
       <c r="E206">
-        <v>-700</v>
+        <v>2200</v>
       </c>
       <c r="F206" t="str">
         <v>2025/2026</v>
@@ -6381,7 +6381,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I206" t="str">
-        <v>Overpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="207">
@@ -6389,19 +6389,19 @@
         <v>UMaT/PG/0206/24</v>
       </c>
       <c r="B207" t="str">
-        <v>Adjoa Ofori</v>
+        <v>Akua Amoah</v>
       </c>
       <c r="C207">
-        <v>13000</v>
+        <v>10900</v>
       </c>
       <c r="D207">
-        <v>8600</v>
+        <v>9900</v>
       </c>
       <c r="E207">
-        <v>4400</v>
+        <v>1000</v>
       </c>
       <c r="F207" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G207" t="str">
         <v>First</v>
@@ -6418,28 +6418,28 @@
         <v>UMaT/PG/0207/24</v>
       </c>
       <c r="B208" t="str">
-        <v>Kwabena Boateng</v>
+        <v>Kwadwo Mensah</v>
       </c>
       <c r="C208">
-        <v>5700</v>
+        <v>7300</v>
       </c>
       <c r="D208">
-        <v>1800</v>
+        <v>7300</v>
       </c>
       <c r="E208">
-        <v>3900</v>
+        <v>0</v>
       </c>
       <c r="F208" t="str">
-        <v>2025/2026</v>
+        <v>2024/2025</v>
       </c>
       <c r="G208" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H208" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I208" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="209">
@@ -6447,28 +6447,28 @@
         <v>UMaT/PG/0208/24</v>
       </c>
       <c r="B209" t="str">
-        <v>Kofi Yeboah</v>
+        <v>Esi Boateng</v>
       </c>
       <c r="C209">
-        <v>8400</v>
+        <v>11400</v>
       </c>
       <c r="D209">
-        <v>8400</v>
+        <v>3500</v>
       </c>
       <c r="E209">
-        <v>0</v>
+        <v>7900</v>
       </c>
       <c r="F209" t="str">
         <v>2025/2026</v>
       </c>
       <c r="G209" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H209" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I209" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="210">
@@ -6476,28 +6476,28 @@
         <v>UMaT/PG/0209/24</v>
       </c>
       <c r="B210" t="str">
-        <v>Efua Nkrumah</v>
+        <v>Adjoa Sarpong</v>
       </c>
       <c r="C210">
-        <v>5000</v>
+        <v>7800</v>
       </c>
       <c r="D210">
-        <v>5000</v>
+        <v>6500</v>
       </c>
       <c r="E210">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="F210" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G210" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H210" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I210" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="211">
@@ -6505,28 +6505,28 @@
         <v>UMaT/PG/0210/24</v>
       </c>
       <c r="B211" t="str">
-        <v>Kwesi Darko</v>
+        <v>Kwadwo Quaye</v>
       </c>
       <c r="C211">
-        <v>8000</v>
+        <v>7500</v>
       </c>
       <c r="D211">
-        <v>3800</v>
+        <v>0</v>
       </c>
       <c r="E211">
-        <v>4200</v>
+        <v>7500</v>
       </c>
       <c r="F211" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G211" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H211" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I211" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="212">
@@ -6534,28 +6534,28 @@
         <v>UMaT/PG/0211/24</v>
       </c>
       <c r="B212" t="str">
-        <v>Akosua Wiredu</v>
+        <v>Adjoa Asante</v>
       </c>
       <c r="C212">
-        <v>6700</v>
+        <v>5800</v>
       </c>
       <c r="D212">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="E212">
-        <v>6700</v>
+        <v>0</v>
       </c>
       <c r="F212" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G212" t="str">
         <v>First</v>
       </c>
       <c r="H212" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I212" t="str">
-        <v>Unpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="213">
@@ -6563,28 +6563,28 @@
         <v>UMaT/PG/0212/24</v>
       </c>
       <c r="B213" t="str">
-        <v>Mansa Wiredu</v>
+        <v>Mensah Acheampong</v>
       </c>
       <c r="C213">
-        <v>7600</v>
+        <v>9800</v>
       </c>
       <c r="D213">
-        <v>7200</v>
+        <v>0</v>
       </c>
       <c r="E213">
-        <v>400</v>
+        <v>9800</v>
       </c>
       <c r="F213" t="str">
         <v>2024/2025</v>
       </c>
       <c r="G213" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H213" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I213" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="214">
@@ -6592,16 +6592,16 @@
         <v>UMaT/PG/0213/24</v>
       </c>
       <c r="B214" t="str">
-        <v>Kobina Asante</v>
+        <v>Kofi Quaye</v>
       </c>
       <c r="C214">
-        <v>9500</v>
+        <v>11800</v>
       </c>
       <c r="D214">
-        <v>9500</v>
+        <v>4100</v>
       </c>
       <c r="E214">
-        <v>0</v>
+        <v>7700</v>
       </c>
       <c r="F214" t="str">
         <v>2025/2026</v>
@@ -6613,7 +6613,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I214" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="215">
@@ -6621,19 +6621,19 @@
         <v>UMaT/PG/0214/24</v>
       </c>
       <c r="B215" t="str">
-        <v>Kakra Amankwah</v>
+        <v>Kwaku Osei</v>
       </c>
       <c r="C215">
-        <v>11400</v>
+        <v>5200</v>
       </c>
       <c r="D215">
-        <v>6600</v>
+        <v>5200</v>
       </c>
       <c r="E215">
-        <v>4800</v>
+        <v>0</v>
       </c>
       <c r="F215" t="str">
-        <v>2025/2026</v>
+        <v>2024/2025</v>
       </c>
       <c r="G215" t="str">
         <v>First</v>
@@ -6642,7 +6642,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I215" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="216">
@@ -6650,19 +6650,19 @@
         <v>UMaT/PG/0215/24</v>
       </c>
       <c r="B216" t="str">
-        <v>Yaa Afriyie</v>
+        <v>Kojo Akuffo</v>
       </c>
       <c r="C216">
-        <v>9700</v>
+        <v>11200</v>
       </c>
       <c r="D216">
         <v>0</v>
       </c>
       <c r="E216">
-        <v>9700</v>
+        <v>11200</v>
       </c>
       <c r="F216" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G216" t="str">
         <v>Second</v>
@@ -6679,19 +6679,19 @@
         <v>UMaT/PG/0216/24</v>
       </c>
       <c r="B217" t="str">
-        <v>Kwadwo Annan</v>
+        <v>Kobina Nkrumah</v>
       </c>
       <c r="C217">
-        <v>9000</v>
+        <v>5500</v>
       </c>
       <c r="D217">
-        <v>10000</v>
+        <v>5500</v>
       </c>
       <c r="E217">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="F217" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G217" t="str">
         <v>First</v>
@@ -6700,7 +6700,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I217" t="str">
-        <v>Overpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="218">
@@ -6708,28 +6708,28 @@
         <v>UMaT/PG/0217/24</v>
       </c>
       <c r="B218" t="str">
-        <v>Kodwo Appiah</v>
+        <v>Araba Asante</v>
       </c>
       <c r="C218">
-        <v>10100</v>
+        <v>7800</v>
       </c>
       <c r="D218">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="E218">
-        <v>10100</v>
+        <v>0</v>
       </c>
       <c r="F218" t="str">
         <v>2025/2026</v>
       </c>
       <c r="G218" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H218" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I218" t="str">
-        <v>Unpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="219">
@@ -6737,22 +6737,22 @@
         <v>UMaT/PG/0218/24</v>
       </c>
       <c r="B219" t="str">
-        <v>Ama Amoah</v>
+        <v>Afi Amoah</v>
       </c>
       <c r="C219">
-        <v>10200</v>
+        <v>12700</v>
       </c>
       <c r="D219">
-        <v>4900</v>
+        <v>10900</v>
       </c>
       <c r="E219">
-        <v>5300</v>
+        <v>1800</v>
       </c>
       <c r="F219" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G219" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H219" t="str">
         <v>Bank Transfer</v>
@@ -6766,28 +6766,28 @@
         <v>UMaT/PG/0219/24</v>
       </c>
       <c r="B220" t="str">
-        <v>Kwame Mensah</v>
+        <v>Yaa Danquah</v>
       </c>
       <c r="C220">
-        <v>12600</v>
+        <v>11800</v>
       </c>
       <c r="D220">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="E220">
-        <v>6600</v>
+        <v>11800</v>
       </c>
       <c r="F220" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G220" t="str">
         <v>Second</v>
       </c>
       <c r="H220" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I220" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="221">
@@ -6795,13 +6795,13 @@
         <v>UMaT/PG/0220/24</v>
       </c>
       <c r="B221" t="str">
-        <v>Kwabena Asante</v>
+        <v>Ama Darko</v>
       </c>
       <c r="C221">
-        <v>9300</v>
+        <v>9100</v>
       </c>
       <c r="D221">
-        <v>9300</v>
+        <v>9100</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -6810,7 +6810,7 @@
         <v>2024/2025</v>
       </c>
       <c r="G221" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H221" t="str">
         <v>Bank Transfer</v>
@@ -6824,22 +6824,22 @@
         <v>UMaT/PG/0221/24</v>
       </c>
       <c r="B222" t="str">
-        <v>Kofi Addo</v>
+        <v>Afia Wiredu</v>
       </c>
       <c r="C222">
-        <v>8300</v>
+        <v>9400</v>
       </c>
       <c r="D222">
-        <v>8300</v>
+        <v>9400</v>
       </c>
       <c r="E222">
         <v>0</v>
       </c>
       <c r="F222" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G222" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H222" t="str">
         <v>Bank Transfer</v>
@@ -6853,19 +6853,19 @@
         <v>UMaT/PG/0222/24</v>
       </c>
       <c r="B223" t="str">
-        <v>Abena Asante</v>
+        <v>Kwadwo Ofori</v>
       </c>
       <c r="C223">
-        <v>5300</v>
+        <v>12800</v>
       </c>
       <c r="D223">
-        <v>3700</v>
+        <v>12800</v>
       </c>
       <c r="E223">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="F223" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G223" t="str">
         <v>Second</v>
@@ -6874,7 +6874,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I223" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="224">
@@ -6882,22 +6882,22 @@
         <v>UMaT/PG/0223/24</v>
       </c>
       <c r="B224" t="str">
-        <v>Kwesi Afriyie</v>
+        <v>Kwame Amoah</v>
       </c>
       <c r="C224">
-        <v>12700</v>
+        <v>8400</v>
       </c>
       <c r="D224">
-        <v>8700</v>
+        <v>4100</v>
       </c>
       <c r="E224">
-        <v>4000</v>
+        <v>4300</v>
       </c>
       <c r="F224" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G224" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H224" t="str">
         <v>Bank Transfer</v>
@@ -6911,19 +6911,19 @@
         <v>UMaT/PG/0224/24</v>
       </c>
       <c r="B225" t="str">
-        <v>Araba Mensah</v>
+        <v>Serwa Addo</v>
       </c>
       <c r="C225">
-        <v>6700</v>
+        <v>8300</v>
       </c>
       <c r="D225">
-        <v>7900</v>
+        <v>3100</v>
       </c>
       <c r="E225">
-        <v>-1200</v>
+        <v>5200</v>
       </c>
       <c r="F225" t="str">
-        <v>2025/2026</v>
+        <v>2024/2025</v>
       </c>
       <c r="G225" t="str">
         <v>Second</v>
@@ -6932,7 +6932,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I225" t="str">
-        <v>Overpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="226">
@@ -6940,28 +6940,28 @@
         <v>UMaT/PG/0225/24</v>
       </c>
       <c r="B226" t="str">
-        <v>Kwabena Frimpong</v>
+        <v>Akua Afriyie</v>
       </c>
       <c r="C226">
-        <v>6600</v>
+        <v>7700</v>
       </c>
       <c r="D226">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="E226">
-        <v>2100</v>
+        <v>7700</v>
       </c>
       <c r="F226" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G226" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H226" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I226" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="227">
@@ -6969,28 +6969,28 @@
         <v>UMaT/PG/0226/24</v>
       </c>
       <c r="B227" t="str">
-        <v>Ama Annan</v>
+        <v>Araba Nkrumah</v>
       </c>
       <c r="C227">
-        <v>8900</v>
+        <v>7100</v>
       </c>
       <c r="D227">
-        <v>8900</v>
+        <v>5900</v>
       </c>
       <c r="E227">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="F227" t="str">
         <v>2023/2024</v>
       </c>
       <c r="G227" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H227" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I227" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="228">
@@ -6998,28 +6998,28 @@
         <v>UMaT/PG/0227/24</v>
       </c>
       <c r="B228" t="str">
-        <v>Panyin Agyei</v>
+        <v>Yaa Yeboah</v>
       </c>
       <c r="C228">
-        <v>12900</v>
+        <v>6900</v>
       </c>
       <c r="D228">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="E228">
-        <v>12900</v>
+        <v>500</v>
       </c>
       <c r="F228" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G228" t="str">
         <v>First</v>
       </c>
       <c r="H228" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I228" t="str">
-        <v>Unpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="229">
@@ -7027,28 +7027,28 @@
         <v>UMaT/PG/0228/24</v>
       </c>
       <c r="B229" t="str">
-        <v>Yaw Ofori</v>
+        <v>Kakra Amoah</v>
       </c>
       <c r="C229">
-        <v>11000</v>
+        <v>5900</v>
       </c>
       <c r="D229">
-        <v>6100</v>
+        <v>5900</v>
       </c>
       <c r="E229">
-        <v>4900</v>
+        <v>0</v>
       </c>
       <c r="F229" t="str">
-        <v>2025/2026</v>
+        <v>2024/2025</v>
       </c>
       <c r="G229" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H229" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I229" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="230">
@@ -7056,28 +7056,28 @@
         <v>UMaT/PG/0229/24</v>
       </c>
       <c r="B230" t="str">
-        <v>Kodwo Darko</v>
+        <v>Kobina Mensah</v>
       </c>
       <c r="C230">
-        <v>12400</v>
+        <v>7400</v>
       </c>
       <c r="D230">
-        <v>12400</v>
+        <v>5300</v>
       </c>
       <c r="E230">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="F230" t="str">
         <v>2023/2024</v>
       </c>
       <c r="G230" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H230" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I230" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="231">
@@ -7085,16 +7085,16 @@
         <v>UMaT/PG/0230/24</v>
       </c>
       <c r="B231" t="str">
-        <v>Afia Boateng</v>
+        <v>Kwaku Afriyie</v>
       </c>
       <c r="C231">
-        <v>11200</v>
+        <v>6500</v>
       </c>
       <c r="D231">
-        <v>9500</v>
+        <v>0</v>
       </c>
       <c r="E231">
-        <v>1700</v>
+        <v>6500</v>
       </c>
       <c r="F231" t="str">
         <v>2024/2025</v>
@@ -7103,10 +7103,10 @@
         <v>Second</v>
       </c>
       <c r="H231" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I231" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="232">
@@ -7114,16 +7114,16 @@
         <v>UMaT/PG/0231/24</v>
       </c>
       <c r="B232" t="str">
-        <v>Serwa Amoah</v>
+        <v>Yaw Owusu</v>
       </c>
       <c r="C232">
-        <v>10700</v>
+        <v>7500</v>
       </c>
       <c r="D232">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="E232">
-        <v>-1300</v>
+        <v>7500</v>
       </c>
       <c r="F232" t="str">
         <v>2025/2026</v>
@@ -7132,10 +7132,10 @@
         <v>First</v>
       </c>
       <c r="H232" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I232" t="str">
-        <v>Overpaid</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="233">
@@ -7143,22 +7143,22 @@
         <v>UMaT/PG/0232/24</v>
       </c>
       <c r="B233" t="str">
-        <v>Panyin Asante</v>
+        <v>Serwa Mensah</v>
       </c>
       <c r="C233">
-        <v>11700</v>
+        <v>12300</v>
       </c>
       <c r="D233">
-        <v>11700</v>
+        <v>12300</v>
       </c>
       <c r="E233">
         <v>0</v>
       </c>
       <c r="F233" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G233" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H233" t="str">
         <v>Bank Transfer</v>
@@ -7172,19 +7172,19 @@
         <v>UMaT/PG/0233/24</v>
       </c>
       <c r="B234" t="str">
-        <v>Kwaku Sarpong</v>
+        <v>Mansa Ofori</v>
       </c>
       <c r="C234">
-        <v>8000</v>
+        <v>12900</v>
       </c>
       <c r="D234">
-        <v>6800</v>
+        <v>12900</v>
       </c>
       <c r="E234">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="F234" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G234" t="str">
         <v>First</v>
@@ -7193,7 +7193,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I234" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="235">
@@ -7201,28 +7201,28 @@
         <v>UMaT/PG/0234/24</v>
       </c>
       <c r="B235" t="str">
-        <v>Ekua Acheampong</v>
+        <v>Ebo Sarpong</v>
       </c>
       <c r="C235">
-        <v>7600</v>
+        <v>9400</v>
       </c>
       <c r="D235">
-        <v>0</v>
+        <v>9400</v>
       </c>
       <c r="E235">
-        <v>7600</v>
+        <v>0</v>
       </c>
       <c r="F235" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G235" t="str">
         <v>First</v>
       </c>
       <c r="H235" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I235" t="str">
-        <v>Unpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="236">
@@ -7230,28 +7230,28 @@
         <v>UMaT/PG/0235/24</v>
       </c>
       <c r="B236" t="str">
-        <v>Ama Opoku</v>
+        <v>Akosua Nkrumah</v>
       </c>
       <c r="C236">
-        <v>5700</v>
+        <v>9000</v>
       </c>
       <c r="D236">
-        <v>2900</v>
+        <v>0</v>
       </c>
       <c r="E236">
-        <v>2800</v>
+        <v>9000</v>
       </c>
       <c r="F236" t="str">
-        <v>2025/2026</v>
+        <v>2024/2025</v>
       </c>
       <c r="G236" t="str">
         <v>Second</v>
       </c>
       <c r="H236" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I236" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="237">
@@ -7259,13 +7259,13 @@
         <v>UMaT/PG/0236/24</v>
       </c>
       <c r="B237" t="str">
-        <v>Kwabena Boateng</v>
+        <v>Kobina Frimpong</v>
       </c>
       <c r="C237">
-        <v>9600</v>
+        <v>11600</v>
       </c>
       <c r="D237">
-        <v>9600</v>
+        <v>11600</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -7274,7 +7274,7 @@
         <v>2024/2025</v>
       </c>
       <c r="G237" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H237" t="str">
         <v>Bank Transfer</v>
@@ -7288,19 +7288,19 @@
         <v>UMaT/PG/0237/24</v>
       </c>
       <c r="B238" t="str">
-        <v>Esi Akuffo</v>
+        <v>Kakra Agyemang</v>
       </c>
       <c r="C238">
-        <v>10500</v>
+        <v>7200</v>
       </c>
       <c r="D238">
-        <v>10500</v>
+        <v>4700</v>
       </c>
       <c r="E238">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="F238" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G238" t="str">
         <v>First</v>
@@ -7309,7 +7309,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I238" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="239">
@@ -7317,28 +7317,28 @@
         <v>UMaT/PG/0238/24</v>
       </c>
       <c r="B239" t="str">
-        <v>Serwa Wiredu</v>
+        <v>Efua Darko</v>
       </c>
       <c r="C239">
-        <v>6500</v>
+        <v>9500</v>
       </c>
       <c r="D239">
-        <v>4300</v>
+        <v>11100</v>
       </c>
       <c r="E239">
-        <v>2200</v>
+        <v>-1600</v>
       </c>
       <c r="F239" t="str">
         <v>2025/2026</v>
       </c>
       <c r="G239" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H239" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I239" t="str">
-        <v>Partial</v>
+        <v>Overpaid</v>
       </c>
     </row>
     <row r="240">
@@ -7346,28 +7346,28 @@
         <v>UMaT/PG/0239/24</v>
       </c>
       <c r="B240" t="str">
-        <v>Ekua Mensah</v>
+        <v>Adwoa Danquah</v>
       </c>
       <c r="C240">
-        <v>6900</v>
+        <v>12600</v>
       </c>
       <c r="D240">
-        <v>3100</v>
+        <v>12600</v>
       </c>
       <c r="E240">
-        <v>3800</v>
+        <v>0</v>
       </c>
       <c r="F240" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G240" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H240" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I240" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="241">
@@ -7375,19 +7375,19 @@
         <v>UMaT/PG/0240/24</v>
       </c>
       <c r="B241" t="str">
-        <v>Ekua Ofori</v>
+        <v>Serwa Amankwah</v>
       </c>
       <c r="C241">
-        <v>6000</v>
+        <v>11200</v>
       </c>
       <c r="D241">
-        <v>6000</v>
+        <v>4600</v>
       </c>
       <c r="E241">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="F241" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G241" t="str">
         <v>Second</v>
@@ -7396,7 +7396,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I241" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="242">
@@ -7404,28 +7404,28 @@
         <v>UMaT/PG/0241/24</v>
       </c>
       <c r="B242" t="str">
-        <v>Kwesi Danquah</v>
+        <v>Serwa Ofori</v>
       </c>
       <c r="C242">
-        <v>8200</v>
+        <v>7000</v>
       </c>
       <c r="D242">
-        <v>8200</v>
+        <v>8100</v>
       </c>
       <c r="E242">
-        <v>0</v>
+        <v>-1100</v>
       </c>
       <c r="F242" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G242" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H242" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I242" t="str">
-        <v>Paid</v>
+        <v>Overpaid</v>
       </c>
     </row>
     <row r="243">
@@ -7433,19 +7433,19 @@
         <v>UMaT/PG/0242/24</v>
       </c>
       <c r="B243" t="str">
-        <v>Kodwo Frimpong</v>
+        <v>Afia Agyei</v>
       </c>
       <c r="C243">
-        <v>6300</v>
+        <v>9300</v>
       </c>
       <c r="D243">
-        <v>1800</v>
+        <v>9300</v>
       </c>
       <c r="E243">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="F243" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G243" t="str">
         <v>Second</v>
@@ -7454,7 +7454,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I243" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="244">
@@ -7462,28 +7462,28 @@
         <v>UMaT/PG/0243/24</v>
       </c>
       <c r="B244" t="str">
-        <v>Kodwo Amankwah</v>
+        <v>Serwa Sarpong</v>
       </c>
       <c r="C244">
-        <v>12600</v>
+        <v>5200</v>
       </c>
       <c r="D244">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="E244">
-        <v>12600</v>
+        <v>0</v>
       </c>
       <c r="F244" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G244" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H244" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I244" t="str">
-        <v>Unpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="245">
@@ -7491,19 +7491,19 @@
         <v>UMaT/PG/0244/24</v>
       </c>
       <c r="B245" t="str">
-        <v>Kobina Ofori</v>
+        <v>Akosua Afriyie</v>
       </c>
       <c r="C245">
-        <v>12600</v>
+        <v>6100</v>
       </c>
       <c r="D245">
         <v>0</v>
       </c>
       <c r="E245">
-        <v>12600</v>
+        <v>6100</v>
       </c>
       <c r="F245" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G245" t="str">
         <v>Second</v>
@@ -7520,28 +7520,28 @@
         <v>UMaT/PG/0245/24</v>
       </c>
       <c r="B246" t="str">
-        <v>Kobina Boateng</v>
+        <v>Kwaku Darko</v>
       </c>
       <c r="C246">
-        <v>7700</v>
+        <v>11800</v>
       </c>
       <c r="D246">
-        <v>2100</v>
+        <v>11800</v>
       </c>
       <c r="E246">
-        <v>5600</v>
+        <v>0</v>
       </c>
       <c r="F246" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G246" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H246" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I246" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="247">
@@ -7549,13 +7549,13 @@
         <v>UMaT/PG/0246/24</v>
       </c>
       <c r="B247" t="str">
-        <v>Akosua Nkrumah</v>
+        <v>Kwadwo Boakye</v>
       </c>
       <c r="C247">
-        <v>12200</v>
+        <v>10000</v>
       </c>
       <c r="D247">
-        <v>12200</v>
+        <v>10000</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -7578,16 +7578,16 @@
         <v>UMaT/PG/0247/24</v>
       </c>
       <c r="B248" t="str">
-        <v>Yaa Gyasi</v>
+        <v>Serwa Mensah</v>
       </c>
       <c r="C248">
-        <v>9700</v>
+        <v>8400</v>
       </c>
       <c r="D248">
-        <v>0</v>
+        <v>8400</v>
       </c>
       <c r="E248">
-        <v>9700</v>
+        <v>0</v>
       </c>
       <c r="F248" t="str">
         <v>2025/2026</v>
@@ -7596,10 +7596,10 @@
         <v>First</v>
       </c>
       <c r="H248" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I248" t="str">
-        <v>Unpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="249">
@@ -7607,28 +7607,28 @@
         <v>UMaT/PG/0248/24</v>
       </c>
       <c r="B249" t="str">
-        <v>Kodwo Sarpong</v>
+        <v>Yaa Ansah</v>
       </c>
       <c r="C249">
-        <v>8600</v>
+        <v>5600</v>
       </c>
       <c r="D249">
-        <v>8600</v>
+        <v>0</v>
       </c>
       <c r="E249">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="F249" t="str">
         <v>2023/2024</v>
       </c>
       <c r="G249" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H249" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I249" t="str">
-        <v>Paid</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="250">
@@ -7636,19 +7636,19 @@
         <v>UMaT/PG/0249/24</v>
       </c>
       <c r="B250" t="str">
-        <v>Adwoa Nkrumah</v>
+        <v>Abena Boakye</v>
       </c>
       <c r="C250">
-        <v>12800</v>
+        <v>10400</v>
       </c>
       <c r="D250">
-        <v>12800</v>
+        <v>3800</v>
       </c>
       <c r="E250">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="F250" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G250" t="str">
         <v>First</v>
@@ -7657,7 +7657,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I250" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="251">
@@ -7665,28 +7665,28 @@
         <v>UMaT/PG/0250/24</v>
       </c>
       <c r="B251" t="str">
-        <v>Afi Boateng</v>
+        <v>Kwame Gyasi</v>
       </c>
       <c r="C251">
-        <v>8900</v>
+        <v>7300</v>
       </c>
       <c r="D251">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="E251">
-        <v>8900</v>
+        <v>2000</v>
       </c>
       <c r="F251" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G251" t="str">
         <v>First</v>
       </c>
       <c r="H251" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I251" t="str">
-        <v>Unpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="252">
@@ -7694,28 +7694,28 @@
         <v>UMaT/PG/0251/24</v>
       </c>
       <c r="B252" t="str">
-        <v>Ato Agyemang</v>
+        <v>Kwame Gyasi</v>
       </c>
       <c r="C252">
-        <v>7800</v>
+        <v>9100</v>
       </c>
       <c r="D252">
-        <v>0</v>
+        <v>9100</v>
       </c>
       <c r="E252">
-        <v>7800</v>
+        <v>0</v>
       </c>
       <c r="F252" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G252" t="str">
         <v>Second</v>
       </c>
       <c r="H252" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I252" t="str">
-        <v>Unpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="253">
@@ -7723,28 +7723,28 @@
         <v>UMaT/PG/0252/24</v>
       </c>
       <c r="B253" t="str">
-        <v>Afia Mensah</v>
+        <v>Kwadwo Danquah</v>
       </c>
       <c r="C253">
-        <v>8300</v>
+        <v>8900</v>
       </c>
       <c r="D253">
-        <v>7400</v>
+        <v>8900</v>
       </c>
       <c r="E253">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F253" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G253" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H253" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I253" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="254">
@@ -7752,19 +7752,19 @@
         <v>UMaT/PG/0253/24</v>
       </c>
       <c r="B254" t="str">
-        <v>Kwame Danquah</v>
+        <v>Yaa Danquah</v>
       </c>
       <c r="C254">
-        <v>5100</v>
+        <v>5700</v>
       </c>
       <c r="D254">
-        <v>5100</v>
+        <v>3900</v>
       </c>
       <c r="E254">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="F254" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G254" t="str">
         <v>Second</v>
@@ -7773,7 +7773,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I254" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="255">
@@ -7781,28 +7781,28 @@
         <v>UMaT/PG/0254/24</v>
       </c>
       <c r="B255" t="str">
-        <v>Kojo Quaye</v>
+        <v>Efua Agyemang</v>
       </c>
       <c r="C255">
-        <v>7500</v>
+        <v>11200</v>
       </c>
       <c r="D255">
-        <v>0</v>
+        <v>11200</v>
       </c>
       <c r="E255">
-        <v>7500</v>
+        <v>0</v>
       </c>
       <c r="F255" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G255" t="str">
         <v>First</v>
       </c>
       <c r="H255" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I255" t="str">
-        <v>Unpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="256">
@@ -7810,28 +7810,28 @@
         <v>UMaT/PG/0255/24</v>
       </c>
       <c r="B256" t="str">
-        <v>Ato Amankwah</v>
+        <v>Akosua Adjei</v>
       </c>
       <c r="C256">
-        <v>9700</v>
+        <v>9800</v>
       </c>
       <c r="D256">
-        <v>0</v>
+        <v>9800</v>
       </c>
       <c r="E256">
-        <v>9700</v>
+        <v>0</v>
       </c>
       <c r="F256" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G256" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H256" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I256" t="str">
-        <v>Unpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="257">
@@ -7839,19 +7839,19 @@
         <v>UMaT/PG/0256/24</v>
       </c>
       <c r="B257" t="str">
-        <v>Araba Gyasi</v>
+        <v>Kwadwo Amoah</v>
       </c>
       <c r="C257">
-        <v>9800</v>
+        <v>8300</v>
       </c>
       <c r="D257">
         <v>0</v>
       </c>
       <c r="E257">
-        <v>9800</v>
+        <v>8300</v>
       </c>
       <c r="F257" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G257" t="str">
         <v>Second</v>
@@ -7868,22 +7868,22 @@
         <v>UMaT/PG/0257/24</v>
       </c>
       <c r="B258" t="str">
-        <v>Kakra Adjei</v>
+        <v>Mansa Ofori</v>
       </c>
       <c r="C258">
-        <v>12900</v>
+        <v>8300</v>
       </c>
       <c r="D258">
-        <v>12900</v>
+        <v>8300</v>
       </c>
       <c r="E258">
         <v>0</v>
       </c>
       <c r="F258" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G258" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H258" t="str">
         <v>Bank Transfer</v>
@@ -7897,13 +7897,13 @@
         <v>UMaT/PG/0258/24</v>
       </c>
       <c r="B259" t="str">
-        <v>Akosua Amoah</v>
+        <v>Ebo Amankwah</v>
       </c>
       <c r="C259">
-        <v>11700</v>
+        <v>10300</v>
       </c>
       <c r="D259">
-        <v>11700</v>
+        <v>10300</v>
       </c>
       <c r="E259">
         <v>0</v>
@@ -7912,7 +7912,7 @@
         <v>2025/2026</v>
       </c>
       <c r="G259" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H259" t="str">
         <v>Bank Transfer</v>
@@ -7926,28 +7926,28 @@
         <v>UMaT/PG/0259/24</v>
       </c>
       <c r="B260" t="str">
-        <v>Kwame Nkrumah</v>
+        <v>Kodwo Mensah</v>
       </c>
       <c r="C260">
-        <v>9100</v>
+        <v>7300</v>
       </c>
       <c r="D260">
-        <v>5800</v>
+        <v>8500</v>
       </c>
       <c r="E260">
-        <v>3300</v>
+        <v>-1200</v>
       </c>
       <c r="F260" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G260" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H260" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I260" t="str">
-        <v>Partial</v>
+        <v>Overpaid</v>
       </c>
     </row>
     <row r="261">
@@ -7955,16 +7955,16 @@
         <v>UMaT/PG/0260/24</v>
       </c>
       <c r="B261" t="str">
-        <v>Kwesi Ansah</v>
+        <v>Ato Danquah</v>
       </c>
       <c r="C261">
-        <v>6500</v>
+        <v>5700</v>
       </c>
       <c r="D261">
-        <v>5700</v>
+        <v>5000</v>
       </c>
       <c r="E261">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="F261" t="str">
         <v>2025/2026</v>
@@ -7984,28 +7984,28 @@
         <v>UMaT/PG/0261/24</v>
       </c>
       <c r="B262" t="str">
-        <v>Efua Danquah</v>
+        <v>Kwadwo Acheampong</v>
       </c>
       <c r="C262">
-        <v>10700</v>
+        <v>11300</v>
       </c>
       <c r="D262">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="E262">
-        <v>10700</v>
+        <v>6000</v>
       </c>
       <c r="F262" t="str">
         <v>2023/2024</v>
       </c>
       <c r="G262" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H262" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I262" t="str">
-        <v>Unpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="263">
@@ -8013,28 +8013,28 @@
         <v>UMaT/PG/0262/24</v>
       </c>
       <c r="B263" t="str">
-        <v>Yaw Agyemang</v>
+        <v>Ebo Agyemang</v>
       </c>
       <c r="C263">
-        <v>5100</v>
+        <v>8000</v>
       </c>
       <c r="D263">
-        <v>5100</v>
+        <v>0</v>
       </c>
       <c r="E263">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="F263" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G263" t="str">
         <v>First</v>
       </c>
       <c r="H263" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I263" t="str">
-        <v>Paid</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="264">
@@ -8042,16 +8042,16 @@
         <v>UMaT/PG/0263/24</v>
       </c>
       <c r="B264" t="str">
-        <v>Ama Frimpong</v>
+        <v>Adjoa Sarpong</v>
       </c>
       <c r="C264">
-        <v>5800</v>
+        <v>7300</v>
       </c>
       <c r="D264">
-        <v>5800</v>
+        <v>2000</v>
       </c>
       <c r="E264">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="F264" t="str">
         <v>2023/2024</v>
@@ -8063,7 +8063,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I264" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="265">
@@ -8071,28 +8071,28 @@
         <v>UMaT/PG/0264/24</v>
       </c>
       <c r="B265" t="str">
-        <v>Panyin Boakye</v>
+        <v>Akosua Owusu</v>
       </c>
       <c r="C265">
-        <v>7000</v>
+        <v>9800</v>
       </c>
       <c r="D265">
-        <v>0</v>
+        <v>7300</v>
       </c>
       <c r="E265">
-        <v>7000</v>
+        <v>2500</v>
       </c>
       <c r="F265" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G265" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H265" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I265" t="str">
-        <v>Unpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="266">
@@ -8100,19 +8100,19 @@
         <v>UMaT/PG/0265/24</v>
       </c>
       <c r="B266" t="str">
-        <v>Kwaku Amankwah</v>
+        <v>Ama Darko</v>
       </c>
       <c r="C266">
-        <v>7900</v>
+        <v>7000</v>
       </c>
       <c r="D266">
-        <v>6700</v>
+        <v>7000</v>
       </c>
       <c r="E266">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="F266" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G266" t="str">
         <v>Second</v>
@@ -8121,7 +8121,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I266" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="267">
@@ -8129,28 +8129,28 @@
         <v>UMaT/PG/0266/24</v>
       </c>
       <c r="B267" t="str">
-        <v>Kwesi Agyei</v>
+        <v>Panyin Amankwah</v>
       </c>
       <c r="C267">
-        <v>8600</v>
+        <v>6000</v>
       </c>
       <c r="D267">
-        <v>4300</v>
+        <v>6000</v>
       </c>
       <c r="E267">
-        <v>4300</v>
+        <v>0</v>
       </c>
       <c r="F267" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G267" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H267" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I267" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="268">
@@ -8158,28 +8158,28 @@
         <v>UMaT/PG/0267/24</v>
       </c>
       <c r="B268" t="str">
-        <v>Kojo Gyasi</v>
+        <v>Kodwo Mensah</v>
       </c>
       <c r="C268">
-        <v>6800</v>
+        <v>12700</v>
       </c>
       <c r="D268">
-        <v>8000</v>
+        <v>10300</v>
       </c>
       <c r="E268">
-        <v>-1200</v>
+        <v>2400</v>
       </c>
       <c r="F268" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G268" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H268" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I268" t="str">
-        <v>Overpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="269">
@@ -8187,28 +8187,28 @@
         <v>UMaT/PG/0268/24</v>
       </c>
       <c r="B269" t="str">
-        <v>Panyin Afriyie</v>
+        <v>Akua Boateng</v>
       </c>
       <c r="C269">
-        <v>11200</v>
+        <v>7700</v>
       </c>
       <c r="D269">
-        <v>11200</v>
+        <v>7000</v>
       </c>
       <c r="E269">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F269" t="str">
         <v>2023/2024</v>
       </c>
       <c r="G269" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H269" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I269" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="270">
@@ -8216,16 +8216,16 @@
         <v>UMaT/PG/0269/24</v>
       </c>
       <c r="B270" t="str">
-        <v>Ebo Boakye</v>
+        <v>Kojo Boateng</v>
       </c>
       <c r="C270">
-        <v>6600</v>
+        <v>8300</v>
       </c>
       <c r="D270">
-        <v>6600</v>
+        <v>3700</v>
       </c>
       <c r="E270">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="F270" t="str">
         <v>2023/2024</v>
@@ -8237,7 +8237,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I270" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="271">
@@ -8245,19 +8245,19 @@
         <v>UMaT/PG/0270/24</v>
       </c>
       <c r="B271" t="str">
-        <v>Abena Acheampong</v>
+        <v>Kwame Akuffo</v>
       </c>
       <c r="C271">
-        <v>9700</v>
+        <v>10200</v>
       </c>
       <c r="D271">
-        <v>9700</v>
+        <v>12200</v>
       </c>
       <c r="E271">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="F271" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G271" t="str">
         <v>Second</v>
@@ -8266,7 +8266,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I271" t="str">
-        <v>Paid</v>
+        <v>Overpaid</v>
       </c>
     </row>
     <row r="272">
@@ -8274,28 +8274,28 @@
         <v>UMaT/PG/0271/24</v>
       </c>
       <c r="B272" t="str">
-        <v>Ebo Ansah</v>
+        <v>Kojo Gyasi</v>
       </c>
       <c r="C272">
-        <v>9000</v>
+        <v>5200</v>
       </c>
       <c r="D272">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="E272">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="F272" t="str">
         <v>2024/2025</v>
       </c>
       <c r="G272" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H272" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I272" t="str">
-        <v>Unpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="273">
@@ -8303,22 +8303,22 @@
         <v>UMaT/PG/0272/24</v>
       </c>
       <c r="B273" t="str">
-        <v>Mansa Agyemang</v>
+        <v>Kwame Quaye</v>
       </c>
       <c r="C273">
-        <v>6100</v>
+        <v>8400</v>
       </c>
       <c r="D273">
-        <v>6100</v>
+        <v>8400</v>
       </c>
       <c r="E273">
         <v>0</v>
       </c>
       <c r="F273" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G273" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H273" t="str">
         <v>Bank Transfer</v>
@@ -8332,16 +8332,16 @@
         <v>UMaT/PG/0273/24</v>
       </c>
       <c r="B274" t="str">
-        <v>Yaw Afriyie</v>
+        <v>Kwaku Adjei</v>
       </c>
       <c r="C274">
-        <v>11900</v>
+        <v>12400</v>
       </c>
       <c r="D274">
-        <v>0</v>
+        <v>12400</v>
       </c>
       <c r="E274">
-        <v>11900</v>
+        <v>0</v>
       </c>
       <c r="F274" t="str">
         <v>2023/2024</v>
@@ -8350,10 +8350,10 @@
         <v>First</v>
       </c>
       <c r="H274" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I274" t="str">
-        <v>Unpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="275">
@@ -8361,16 +8361,16 @@
         <v>UMaT/PG/0274/24</v>
       </c>
       <c r="B275" t="str">
-        <v>Mansa Frimpong</v>
+        <v>Adjoa Amankwah</v>
       </c>
       <c r="C275">
-        <v>7300</v>
+        <v>9600</v>
       </c>
       <c r="D275">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="E275">
-        <v>7300</v>
+        <v>0</v>
       </c>
       <c r="F275" t="str">
         <v>2024/2025</v>
@@ -8379,10 +8379,10 @@
         <v>Second</v>
       </c>
       <c r="H275" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I275" t="str">
-        <v>Unpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="276">
@@ -8390,16 +8390,16 @@
         <v>UMaT/PG/0275/24</v>
       </c>
       <c r="B276" t="str">
-        <v>Kakra Amankwah</v>
+        <v>Araba Amoah</v>
       </c>
       <c r="C276">
-        <v>7700</v>
+        <v>8800</v>
       </c>
       <c r="D276">
-        <v>7700</v>
+        <v>4600</v>
       </c>
       <c r="E276">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="F276" t="str">
         <v>2023/2024</v>
@@ -8411,7 +8411,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I276" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="277">
@@ -8419,28 +8419,28 @@
         <v>UMaT/PG/0276/24</v>
       </c>
       <c r="B277" t="str">
-        <v>Ama Boakye</v>
+        <v>Esi Acheampong</v>
       </c>
       <c r="C277">
-        <v>10100</v>
+        <v>5200</v>
       </c>
       <c r="D277">
-        <v>4300</v>
+        <v>0</v>
       </c>
       <c r="E277">
-        <v>5800</v>
+        <v>5200</v>
       </c>
       <c r="F277" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G277" t="str">
         <v>First</v>
       </c>
       <c r="H277" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I277" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="278">
@@ -8448,28 +8448,28 @@
         <v>UMaT/PG/0277/24</v>
       </c>
       <c r="B278" t="str">
-        <v>Ama Wiredu</v>
+        <v>Adwoa Ansah</v>
       </c>
       <c r="C278">
-        <v>6400</v>
+        <v>6000</v>
       </c>
       <c r="D278">
-        <v>6400</v>
+        <v>0</v>
       </c>
       <c r="E278">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="F278" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G278" t="str">
         <v>First</v>
       </c>
       <c r="H278" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I278" t="str">
-        <v>Paid</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="279">
@@ -8477,28 +8477,28 @@
         <v>UMaT/PG/0278/24</v>
       </c>
       <c r="B279" t="str">
-        <v>Mansa Mensah</v>
+        <v>Yaa Agyei</v>
       </c>
       <c r="C279">
-        <v>5100</v>
+        <v>7000</v>
       </c>
       <c r="D279">
-        <v>5100</v>
+        <v>3700</v>
       </c>
       <c r="E279">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="F279" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G279" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H279" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I279" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="280">
@@ -8506,19 +8506,19 @@
         <v>UMaT/PG/0279/24</v>
       </c>
       <c r="B280" t="str">
-        <v>Kwesi Agyemang</v>
+        <v>Mansa Owusu</v>
       </c>
       <c r="C280">
-        <v>9700</v>
+        <v>12600</v>
       </c>
       <c r="D280">
-        <v>10800</v>
+        <v>5300</v>
       </c>
       <c r="E280">
-        <v>-1100</v>
+        <v>7300</v>
       </c>
       <c r="F280" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G280" t="str">
         <v>Second</v>
@@ -8527,7 +8527,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I280" t="str">
-        <v>Overpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="281">
@@ -8535,19 +8535,19 @@
         <v>UMaT/PG/0280/24</v>
       </c>
       <c r="B281" t="str">
-        <v>Abena Darko</v>
+        <v>Akosua Darko</v>
       </c>
       <c r="C281">
-        <v>5300</v>
+        <v>9100</v>
       </c>
       <c r="D281">
-        <v>5300</v>
+        <v>10400</v>
       </c>
       <c r="E281">
-        <v>0</v>
+        <v>-1300</v>
       </c>
       <c r="F281" t="str">
-        <v>2025/2026</v>
+        <v>2024/2025</v>
       </c>
       <c r="G281" t="str">
         <v>First</v>
@@ -8556,7 +8556,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I281" t="str">
-        <v>Paid</v>
+        <v>Overpaid</v>
       </c>
     </row>
     <row r="282">
@@ -8564,28 +8564,28 @@
         <v>UMaT/PG/0281/24</v>
       </c>
       <c r="B282" t="str">
-        <v>Adjoa Sarpong</v>
+        <v>Kwame Amankwah</v>
       </c>
       <c r="C282">
-        <v>8600</v>
+        <v>7400</v>
       </c>
       <c r="D282">
-        <v>0</v>
+        <v>8300</v>
       </c>
       <c r="E282">
-        <v>8600</v>
+        <v>-900</v>
       </c>
       <c r="F282" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G282" t="str">
         <v>Second</v>
       </c>
       <c r="H282" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I282" t="str">
-        <v>Unpaid</v>
+        <v>Overpaid</v>
       </c>
     </row>
     <row r="283">
@@ -8593,16 +8593,16 @@
         <v>UMaT/PG/0282/24</v>
       </c>
       <c r="B283" t="str">
-        <v>Kwaku Amankwah</v>
+        <v>Efua Wiredu</v>
       </c>
       <c r="C283">
-        <v>6600</v>
+        <v>9500</v>
       </c>
       <c r="D283">
-        <v>5300</v>
+        <v>8500</v>
       </c>
       <c r="E283">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="F283" t="str">
         <v>2023/2024</v>
@@ -8622,28 +8622,28 @@
         <v>UMaT/PG/0283/24</v>
       </c>
       <c r="B284" t="str">
-        <v>Mansa Gyasi</v>
+        <v>Araba Agyemang</v>
       </c>
       <c r="C284">
-        <v>5800</v>
+        <v>12300</v>
       </c>
       <c r="D284">
-        <v>5800</v>
+        <v>3200</v>
       </c>
       <c r="E284">
-        <v>0</v>
+        <v>9100</v>
       </c>
       <c r="F284" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G284" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H284" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I284" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="285">
@@ -8651,28 +8651,28 @@
         <v>UMaT/PG/0284/24</v>
       </c>
       <c r="B285" t="str">
-        <v>Yaa Akuffo</v>
+        <v>Araba Osei</v>
       </c>
       <c r="C285">
-        <v>5500</v>
+        <v>11600</v>
       </c>
       <c r="D285">
-        <v>0</v>
+        <v>11600</v>
       </c>
       <c r="E285">
-        <v>5500</v>
+        <v>0</v>
       </c>
       <c r="F285" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G285" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H285" t="str">
-        <v>N/A</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="I285" t="str">
-        <v>Unpaid</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="286">
@@ -8680,7 +8680,7 @@
         <v>UMaT/PG/0285/24</v>
       </c>
       <c r="B286" t="str">
-        <v>Panyin Amankwah</v>
+        <v>Panyin Ansah</v>
       </c>
       <c r="C286">
         <v>11500</v>
@@ -8692,7 +8692,7 @@
         <v>0</v>
       </c>
       <c r="F286" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G286" t="str">
         <v>Second</v>
@@ -8709,19 +8709,19 @@
         <v>UMaT/PG/0286/24</v>
       </c>
       <c r="B287" t="str">
-        <v>Efua Danquah</v>
+        <v>Abena Mensah</v>
       </c>
       <c r="C287">
-        <v>8800</v>
+        <v>9400</v>
       </c>
       <c r="D287">
         <v>0</v>
       </c>
       <c r="E287">
-        <v>8800</v>
+        <v>9400</v>
       </c>
       <c r="F287" t="str">
-        <v>2025/2026</v>
+        <v>2024/2025</v>
       </c>
       <c r="G287" t="str">
         <v>First</v>
@@ -8738,28 +8738,28 @@
         <v>UMaT/PG/0287/24</v>
       </c>
       <c r="B288" t="str">
-        <v>Ama Appiah</v>
+        <v>Kwesi Darko</v>
       </c>
       <c r="C288">
-        <v>8500</v>
+        <v>12500</v>
       </c>
       <c r="D288">
-        <v>6200</v>
+        <v>0</v>
       </c>
       <c r="E288">
-        <v>2300</v>
+        <v>12500</v>
       </c>
       <c r="F288" t="str">
-        <v>2024/2025</v>
+        <v>2025/2026</v>
       </c>
       <c r="G288" t="str">
         <v>Second</v>
       </c>
       <c r="H288" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I288" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="289">
@@ -8767,16 +8767,16 @@
         <v>UMaT/PG/0288/24</v>
       </c>
       <c r="B289" t="str">
-        <v>Kofi Ofori</v>
+        <v>Efua Afriyie</v>
       </c>
       <c r="C289">
-        <v>9400</v>
+        <v>10800</v>
       </c>
       <c r="D289">
-        <v>9400</v>
+        <v>5500</v>
       </c>
       <c r="E289">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="F289" t="str">
         <v>2023/2024</v>
@@ -8788,7 +8788,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I289" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="290">
@@ -8796,28 +8796,28 @@
         <v>UMaT/PG/0289/24</v>
       </c>
       <c r="B290" t="str">
-        <v>Afi Danquah</v>
+        <v>Kakra Quaye</v>
       </c>
       <c r="C290">
-        <v>9700</v>
+        <v>7400</v>
       </c>
       <c r="D290">
-        <v>9700</v>
+        <v>6700</v>
       </c>
       <c r="E290">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F290" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G290" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H290" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I290" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="291">
@@ -8825,16 +8825,16 @@
         <v>UMaT/PG/0290/24</v>
       </c>
       <c r="B291" t="str">
-        <v>Afia Acheampong</v>
+        <v>Afi Quaye</v>
       </c>
       <c r="C291">
-        <v>8400</v>
+        <v>12200</v>
       </c>
       <c r="D291">
-        <v>8800</v>
+        <v>11200</v>
       </c>
       <c r="E291">
-        <v>-400</v>
+        <v>1000</v>
       </c>
       <c r="F291" t="str">
         <v>2025/2026</v>
@@ -8846,7 +8846,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I291" t="str">
-        <v>Overpaid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="292">
@@ -8854,19 +8854,19 @@
         <v>UMaT/PG/0291/24</v>
       </c>
       <c r="B292" t="str">
-        <v>Kwesi Afriyie</v>
+        <v>Ekua Annan</v>
       </c>
       <c r="C292">
-        <v>11300</v>
+        <v>10000</v>
       </c>
       <c r="D292">
-        <v>4900</v>
+        <v>10000</v>
       </c>
       <c r="E292">
-        <v>6400</v>
+        <v>0</v>
       </c>
       <c r="F292" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G292" t="str">
         <v>First</v>
@@ -8875,7 +8875,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I292" t="str">
-        <v>Partial</v>
+        <v>Paid</v>
       </c>
     </row>
     <row r="293">
@@ -8883,28 +8883,28 @@
         <v>UMaT/PG/0292/24</v>
       </c>
       <c r="B293" t="str">
-        <v>Kakra Asante</v>
+        <v>Adwoa Adjei</v>
       </c>
       <c r="C293">
-        <v>9200</v>
+        <v>12900</v>
       </c>
       <c r="D293">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="E293">
-        <v>2200</v>
+        <v>12900</v>
       </c>
       <c r="F293" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G293" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H293" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I293" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="294">
@@ -8912,28 +8912,28 @@
         <v>UMaT/PG/0293/24</v>
       </c>
       <c r="B294" t="str">
-        <v>Araba Owusu</v>
+        <v>Mansa Osei</v>
       </c>
       <c r="C294">
-        <v>8900</v>
+        <v>12300</v>
       </c>
       <c r="D294">
-        <v>8900</v>
+        <v>12900</v>
       </c>
       <c r="E294">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="F294" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G294" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H294" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="I294" t="str">
-        <v>Paid</v>
+        <v>Overpaid</v>
       </c>
     </row>
     <row r="295">
@@ -8941,19 +8941,19 @@
         <v>UMaT/PG/0294/24</v>
       </c>
       <c r="B295" t="str">
-        <v>Ama Quaye</v>
+        <v>Kwesi Asante</v>
       </c>
       <c r="C295">
-        <v>7700</v>
+        <v>10300</v>
       </c>
       <c r="D295">
-        <v>7700</v>
+        <v>10300</v>
       </c>
       <c r="E295">
         <v>0</v>
       </c>
       <c r="F295" t="str">
-        <v>2023/2024</v>
+        <v>2025/2026</v>
       </c>
       <c r="G295" t="str">
         <v>Second</v>
@@ -8970,19 +8970,19 @@
         <v>UMaT/PG/0295/24</v>
       </c>
       <c r="B296" t="str">
-        <v>Abena Quaye</v>
+        <v>Kwadwo Wiredu</v>
       </c>
       <c r="C296">
-        <v>11700</v>
+        <v>11900</v>
       </c>
       <c r="D296">
-        <v>11700</v>
+        <v>9200</v>
       </c>
       <c r="E296">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="F296" t="str">
-        <v>2024/2025</v>
+        <v>2023/2024</v>
       </c>
       <c r="G296" t="str">
         <v>First</v>
@@ -8991,7 +8991,7 @@
         <v>Bank Transfer</v>
       </c>
       <c r="I296" t="str">
-        <v>Paid</v>
+        <v>Partial</v>
       </c>
     </row>
     <row r="297">
@@ -8999,28 +8999,28 @@
         <v>UMaT/PG/0296/24</v>
       </c>
       <c r="B297" t="str">
-        <v>Kwadwo Mensah</v>
+        <v>Kofi Opoku</v>
       </c>
       <c r="C297">
-        <v>5800</v>
+        <v>12800</v>
       </c>
       <c r="D297">
-        <v>5800</v>
+        <v>0</v>
       </c>
       <c r="E297">
-        <v>0</v>
+        <v>12800</v>
       </c>
       <c r="F297" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G297" t="str">
         <v>Second</v>
       </c>
       <c r="H297" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I297" t="str">
-        <v>Paid</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="298">
@@ -9028,28 +9028,28 @@
         <v>UMaT/PG/0297/24</v>
       </c>
       <c r="B298" t="str">
-        <v>Akua Opoku</v>
+        <v>Abena Acheampong</v>
       </c>
       <c r="C298">
-        <v>11800</v>
+        <v>11000</v>
       </c>
       <c r="D298">
-        <v>11800</v>
+        <v>0</v>
       </c>
       <c r="E298">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="F298" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G298" t="str">
-        <v>First</v>
+        <v>Second</v>
       </c>
       <c r="H298" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I298" t="str">
-        <v>Paid</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="299">
@@ -9057,28 +9057,28 @@
         <v>UMaT/PG/0298/24</v>
       </c>
       <c r="B299" t="str">
-        <v>Kojo Osei</v>
+        <v>Kwadwo Ofori</v>
       </c>
       <c r="C299">
-        <v>8400</v>
+        <v>13000</v>
       </c>
       <c r="D299">
-        <v>4600</v>
+        <v>0</v>
       </c>
       <c r="E299">
-        <v>3800</v>
+        <v>13000</v>
       </c>
       <c r="F299" t="str">
-        <v>2025/2026</v>
+        <v>2023/2024</v>
       </c>
       <c r="G299" t="str">
-        <v>Second</v>
+        <v>First</v>
       </c>
       <c r="H299" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I299" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="300">
@@ -9086,28 +9086,28 @@
         <v>UMaT/PG/0299/24</v>
       </c>
       <c r="B300" t="str">
-        <v>Yaa Agyei</v>
+        <v>Adwoa Danquah</v>
       </c>
       <c r="C300">
-        <v>5700</v>
+        <v>11700</v>
       </c>
       <c r="D300">
-        <v>5700</v>
+        <v>0</v>
       </c>
       <c r="E300">
-        <v>0</v>
+        <v>11700</v>
       </c>
       <c r="F300" t="str">
-        <v>2023/2024</v>
+        <v>2024/2025</v>
       </c>
       <c r="G300" t="str">
         <v>First</v>
       </c>
       <c r="H300" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I300" t="str">
-        <v>Paid</v>
+        <v>Unpaid</v>
       </c>
     </row>
     <row r="301">
@@ -9115,16 +9115,16 @@
         <v>UMaT/PG/0300/24</v>
       </c>
       <c r="B301" t="str">
-        <v>Kakra Frimpong</v>
+        <v>Akosua Agyemang</v>
       </c>
       <c r="C301">
-        <v>8300</v>
+        <v>6000</v>
       </c>
       <c r="D301">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="E301">
-        <v>6200</v>
+        <v>6000</v>
       </c>
       <c r="F301" t="str">
         <v>2025/2026</v>
@@ -9133,10 +9133,10 @@
         <v>Second</v>
       </c>
       <c r="H301" t="str">
-        <v>Bank Transfer</v>
+        <v>N/A</v>
       </c>
       <c r="I301" t="str">
-        <v>Partial</v>
+        <v>Unpaid</v>
       </c>
     </row>
   </sheetData>
